--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -2021,7 +2021,7 @@
         <v>1275981</v>
       </c>
       <c r="B13" t="n">
-        <v>86130</v>
+        <v>88128</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spröd vaxskivling</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2052,16 +2052,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R13" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2091,27 +2094,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2120,7 +2114,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2132,11 +2125,7 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2265,7 +2254,7 @@
         <v>1549635</v>
       </c>
       <c r="B15" t="n">
-        <v>86135</v>
+        <v>88133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2282,7 +2271,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Toppvaxskivling</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2296,16 +2285,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R15" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2335,27 +2327,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2364,7 +2347,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2376,18 +2358,14 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>1106707</v>
       </c>
       <c r="B16" t="n">
-        <v>85003</v>
+        <v>88062</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2418,16 +2396,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R16" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2457,27 +2438,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2486,7 +2458,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2498,18 +2469,14 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>1347795</v>
       </c>
       <c r="B17" t="n">
-        <v>86131</v>
+        <v>88129</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2526,7 +2493,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gul vaxskivling</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2540,16 +2507,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R17" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S17" t="n">
         <v>100</v>
@@ -2579,27 +2549,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2608,7 +2569,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr"/>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
@@ -2620,18 +2580,14 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>1102068</v>
       </c>
       <c r="B18" t="n">
-        <v>85001</v>
+        <v>88060</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2662,16 +2618,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R18" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S18" t="n">
         <v>100</v>
@@ -2701,27 +2660,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2730,7 +2680,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
@@ -2742,11 +2691,7 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2875,7 +2820,7 @@
         <v>1428320</v>
       </c>
       <c r="B20" t="n">
-        <v>86133</v>
+        <v>88131</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2892,7 +2837,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2906,16 +2851,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R20" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -2945,27 +2893,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2974,7 +2913,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr"/>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -2986,18 +2924,14 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>1189591</v>
       </c>
       <c r="B21" t="n">
-        <v>86313</v>
+        <v>88326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3024,16 +2958,19 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R21" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S21" t="n">
         <v>100</v>
@@ -3063,27 +3000,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3092,7 +3020,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr"/>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -3104,11 +3031,7 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3233,7 +3156,7 @@
         <v>1221014</v>
       </c>
       <c r="B23" t="n">
-        <v>86160</v>
+        <v>88154</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3250,7 +3173,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Honungsvaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3264,16 +3187,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R23" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3303,27 +3229,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3332,7 +3249,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3344,18 +3260,14 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>1209184</v>
       </c>
       <c r="B24" t="n">
-        <v>86111</v>
+        <v>88108</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3382,16 +3294,19 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R24" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S24" t="n">
         <v>100</v>
@@ -3421,27 +3336,18 @@
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2007-10-03</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3450,7 +3356,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr"/>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
@@ -3462,11 +3367,7 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -2021,7 +2021,7 @@
         <v>1275981</v>
       </c>
       <c r="B13" t="n">
-        <v>88128</v>
+        <v>88310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>1549635</v>
       </c>
       <c r="B15" t="n">
-        <v>88133</v>
+        <v>88315</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>1106707</v>
       </c>
       <c r="B16" t="n">
-        <v>88062</v>
+        <v>88214</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>1347795</v>
       </c>
       <c r="B17" t="n">
-        <v>88129</v>
+        <v>88311</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>1102068</v>
       </c>
       <c r="B18" t="n">
-        <v>88060</v>
+        <v>88212</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>1428320</v>
       </c>
       <c r="B20" t="n">
-        <v>88131</v>
+        <v>88313</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>1189591</v>
       </c>
       <c r="B21" t="n">
-        <v>88326</v>
+        <v>88267</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>1221014</v>
       </c>
       <c r="B23" t="n">
-        <v>88154</v>
+        <v>88336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>1209184</v>
       </c>
       <c r="B24" t="n">
-        <v>88108</v>
+        <v>88290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -2021,7 +2021,7 @@
         <v>1275981</v>
       </c>
       <c r="B13" t="n">
-        <v>88419</v>
+        <v>88426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>1549635</v>
       </c>
       <c r="B15" t="n">
-        <v>88424</v>
+        <v>88431</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>1106707</v>
       </c>
       <c r="B16" t="n">
-        <v>88323</v>
+        <v>88330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>1347795</v>
       </c>
       <c r="B17" t="n">
-        <v>88420</v>
+        <v>88427</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>1102068</v>
       </c>
       <c r="B18" t="n">
-        <v>88321</v>
+        <v>88328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>1428320</v>
       </c>
       <c r="B20" t="n">
-        <v>88422</v>
+        <v>88429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>1189591</v>
       </c>
       <c r="B21" t="n">
-        <v>88376</v>
+        <v>88383</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>1221014</v>
       </c>
       <c r="B23" t="n">
-        <v>88445</v>
+        <v>88452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>1209184</v>
       </c>
       <c r="B24" t="n">
-        <v>88399</v>
+        <v>88406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,12 +2127,7 @@
         <v>1617733</v>
       </c>
       <c r="B14" t="n">
-        <v>86147</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88453</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2139,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småvaxskivling</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2158,16 +2153,18 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R14" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2197,27 +2194,18 @@
           <t>2007-10-20</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2007-10-20</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2238,11 +2226,7 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2673,12 +2657,7 @@
         <v>1096544</v>
       </c>
       <c r="B19" t="n">
-        <v>84999</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2704,16 +2683,18 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R19" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -2743,27 +2724,18 @@
           <t>2007-10-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2007-10-20</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2784,11 +2756,7 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3000,15 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1248020</v>
+        <v>1190063</v>
       </c>
       <c r="B22" t="n">
-        <v>86319</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3016,30 +2979,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4398</v>
+        <v>4392</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
+          <t>Cuphophyllus pratensis s.lat.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436453.112063889</v>
+        <v>436453</v>
       </c>
       <c r="R22" t="n">
-        <v>6419120.225843054</v>
+        <v>6419120</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3069,27 +3034,18 @@
           <t>2007-10-20</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2007-10-20</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3110,18 +3066,14 @@
           <t>Kerstin Bergelin</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1221014</v>
+        <v>1248020</v>
       </c>
       <c r="B23" t="n">
-        <v>88452</v>
+        <v>88395</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3129,25 +3081,20 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4394</v>
+        <v>4398</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3159,7 +3106,7 @@
         <v>436453</v>
       </c>
       <c r="R23" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3186,12 +3133,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2007-10-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2007-10-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,6 +3156,7 @@
           <t>Betesmark</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3224,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1209184</v>
+        <v>1221014</v>
       </c>
       <c r="B24" t="n">
-        <v>88406</v>
+        <v>88452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,19 +3183,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4393</v>
+        <v>4394</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3326,53 +3278,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4535752</v>
+        <v>1247452</v>
       </c>
       <c r="B25" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222112</v>
+        <v>4398</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R25" t="n">
-        <v>6419140.861195157</v>
+        <v>6419121</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,22 +3342,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3420,71 +3356,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>472939</v>
+        <v>1209184</v>
       </c>
       <c r="B26" t="n">
-        <v>104540</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1174</v>
+        <v>4393</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gliophorus psittacinus s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R26" t="n">
-        <v>6419140.861195157</v>
+        <v>6419121</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3508,22 +3444,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,67 +3458,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3873115</v>
+        <v>1096336</v>
       </c>
       <c r="B27" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221447</v>
+        <v>3294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436459.1625334214</v>
+        <v>436453</v>
       </c>
       <c r="R27" t="n">
-        <v>6419098.873399709</v>
+        <v>6419121</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3616,22 +3550,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,25 +3564,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4536303</v>
+        <v>4535752</v>
       </c>
       <c r="B28" t="n">
         <v>95590</v>
@@ -3698,10 +3628,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436459.1625334214</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R28" t="n">
-        <v>6419098.873399709</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3728,7 +3658,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3738,7 +3668,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3770,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2366753</v>
+        <v>472939</v>
       </c>
       <c r="B29" t="n">
-        <v>104837</v>
+        <v>104540</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3782,20 +3712,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219955</v>
+        <v>1174</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3810,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436535.8438908673</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R29" t="n">
-        <v>6419133.262726188</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3840,7 +3770,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3850,7 +3780,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -3882,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>481765</v>
+        <v>3873115</v>
       </c>
       <c r="B30" t="n">
-        <v>104540</v>
+        <v>103426</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3894,50 +3824,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1174</v>
+        <v>221447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäboruder 3, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436508.1585393944</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R30" t="n">
-        <v>6419099.690997186</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3959,14 +3876,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>F-Hab-0069</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3976,17 +3888,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4009,15 +3916,11 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4540051</v>
+        <v>4536303</v>
       </c>
       <c r="B31" t="n">
         <v>95590</v>
@@ -4050,29 +3953,20 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436535.8438908673</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R31" t="n">
-        <v>6419133.262726188</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4096,7 +3990,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4106,7 +4000,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4138,7 +4032,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2337603</v>
+        <v>2366753</v>
       </c>
       <c r="B32" t="n">
         <v>104837</v>
@@ -4174,17 +4068,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436507.2332066745</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R32" t="n">
-        <v>6419175.697058928</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4208,7 +4102,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4218,7 +4112,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4238,26 +4132,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2642441</v>
+        <v>481765</v>
       </c>
       <c r="B33" t="n">
-        <v>106756</v>
+        <v>104540</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4270,16 +4160,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220228</v>
+        <v>1174</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4287,20 +4177,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder 3, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436507.2332066745</v>
+        <v>436508.1585393944</v>
       </c>
       <c r="R33" t="n">
-        <v>6419175.697058928</v>
+        <v>6419099.690997186</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4322,9 +4221,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>F-Hab-0069</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4334,12 +4238,17 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4354,26 +4263,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Västergötlands flora 2002</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3849133</v>
+        <v>4540051</v>
       </c>
       <c r="B34" t="n">
-        <v>103426</v>
+        <v>95590</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4382,37 +4291,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221447</v>
+        <v>222112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436406.0461207972</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R34" t="n">
-        <v>6419274.547413215</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4436,7 +4358,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4446,7 +4368,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4466,26 +4388,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>453603</v>
+        <v>2337603</v>
       </c>
       <c r="B35" t="n">
-        <v>104540</v>
+        <v>104837</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4494,20 +4412,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4518,7 +4436,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4552,7 +4470,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4562,7 +4480,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4587,7 +4505,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4598,10 +4516,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4531256</v>
+        <v>2642441</v>
       </c>
       <c r="B36" t="n">
-        <v>95590</v>
+        <v>106756</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4614,27 +4532,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222112</v>
+        <v>220228</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4668,7 +4586,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4678,7 +4596,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4703,7 +4621,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4714,10 +4632,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>467027</v>
+        <v>3849133</v>
       </c>
       <c r="B37" t="n">
-        <v>104541</v>
+        <v>103426</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4726,41 +4644,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1174</v>
+        <v>221447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436502.7055573605</v>
+        <v>436406.0461207972</v>
       </c>
       <c r="R37" t="n">
-        <v>6419158.763860945</v>
+        <v>6419274.547413215</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4784,7 +4698,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4794,17 +4708,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4819,22 +4728,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Isaksson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Anna Isaksson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>75339585</v>
+        <v>453603</v>
       </c>
       <c r="B38" t="n">
-        <v>108526</v>
+        <v>104540</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4847,16 +4760,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220204</v>
+        <v>1174</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4865,20 +4778,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436529</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R38" t="n">
-        <v>6419163</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -4905,17 +4814,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>1997-06-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>1997-06-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4924,90 +4838,75 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Västergötlands flora 2002</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>437488</v>
+        <v>4531256</v>
       </c>
       <c r="B39" t="n">
-        <v>76591</v>
+        <v>95590</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1591</v>
+        <v>222112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knubbig hårjordtunga</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichoglossum walteri</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk.) E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436542.2437137502</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R39" t="n">
-        <v>6419201.181122187</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5031,7 +4930,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5041,7 +4940,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5058,31 +4957,29 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Gösta Börjeson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>75773478</v>
+        <v>467027</v>
       </c>
       <c r="B40" t="n">
-        <v>104838</v>
+        <v>104541</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5091,20 +4988,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219955</v>
+        <v>1174</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5115,17 +5012,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäboruder 5, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436529.3954344561</v>
+        <v>436502.7055573605</v>
       </c>
       <c r="R40" t="n">
-        <v>6419163.123649723</v>
+        <v>6419158.763860945</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5147,14 +5044,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>F-Hab-0342</t>
-        </is>
-      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5164,12 +5056,17 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5184,30 +5081,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anna Isaksson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Via Anna Isaksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>310069</v>
+        <v>75339585</v>
       </c>
       <c r="B41" t="n">
-        <v>86117</v>
+        <v>108526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5216,34 +5109,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>803</v>
+        <v>220204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436453.112063889</v>
+        <v>436529</v>
       </c>
       <c r="R41" t="n">
-        <v>6419120.225843054</v>
+        <v>6419163</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
@@ -5270,22 +5167,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5294,38 +5186,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr"/>
+          <t>Betesmark-häst</t>
+        </is>
+      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>ÅGP inventering</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>576272</v>
+        <v>437488</v>
       </c>
       <c r="B42" t="n">
-        <v>107333</v>
+        <v>76591</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5338,37 +5230,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1758</v>
+        <v>1591</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Knubbig hårjordtunga</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Trichoglossum walteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Berk.) E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436459.1625334214</v>
+        <v>436542.2437137502</v>
       </c>
       <c r="R42" t="n">
-        <v>6419098.873399709</v>
+        <v>6419201.181122187</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5392,7 +5293,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5402,7 +5303,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5419,29 +5320,35 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>576271</v>
+        <v>75773478</v>
       </c>
       <c r="B43" t="n">
-        <v>107333</v>
+        <v>104838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5450,34 +5357,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1758</v>
+        <v>219955</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 5, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436473.7803032578</v>
+        <v>436529.3954344561</v>
       </c>
       <c r="R43" t="n">
-        <v>6419080.573521676</v>
+        <v>6419163.123649723</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5502,9 +5409,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>F-Hab-0342</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5514,7 +5426,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5522,11 +5434,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5535,31 +5442,30 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>576247</v>
+        <v>310069</v>
       </c>
       <c r="B44" t="n">
-        <v>107333</v>
+        <v>86117</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5568,41 +5474,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1758</v>
+        <v>803</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Lutvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäboruder 1, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436519.3450587477</v>
+        <v>436453.112063889</v>
       </c>
       <c r="R44" t="n">
-        <v>6419100.045175258</v>
+        <v>6419120.225843054</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5624,14 +5530,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>F-Hab-0065</t>
-        </is>
-      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5641,7 +5542,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5649,11 +5550,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Mycket blad bör kollas nästa år</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5668,76 +5564,73 @@
           <t>Betesmark</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr"/>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>ÅGP inventering</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>86334010</v>
+        <v>576272</v>
       </c>
       <c r="B45" t="n">
-        <v>106757</v>
+        <v>107333</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220228</v>
+        <v>1758</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436458.7635083896</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R45" t="n">
-        <v>6419140.861195157</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5761,7 +5654,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5771,7 +5664,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5785,14 +5678,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5809,7 +5696,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>86334843</v>
+        <v>576271</v>
       </c>
       <c r="B46" t="n">
         <v>107333</v>
@@ -5842,29 +5729,17 @@
           <t>H. Lindb.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäboruder 6, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436572.0813967428</v>
+        <v>436473.7803032578</v>
       </c>
       <c r="R46" t="n">
-        <v>6419135.34599164</v>
+        <v>6419080.573521676</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5889,14 +5764,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>F-Hab-0701</t>
-        </is>
-      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5906,7 +5776,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -5914,83 +5784,87 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103768145</v>
+        <v>576247</v>
       </c>
       <c r="B47" t="n">
-        <v>86159</v>
+        <v>107333</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>806</v>
+        <v>1758</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder 1, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436381.4818315752</v>
+        <v>436519.3450587477</v>
       </c>
       <c r="R47" t="n">
-        <v>6419102.23161179</v>
+        <v>6419100.045175258</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6012,24 +5886,34 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>F-Hab-0065</t>
+        </is>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mycket blad bör kollas nästa år</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6040,26 +5924,35 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103769665</v>
+        <v>86334010</v>
       </c>
       <c r="B48" t="n">
-        <v>86110</v>
+        <v>106757</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6068,42 +5961,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>239221</v>
+        <v>220228</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Herink</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436345.3451666282</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R48" t="n">
-        <v>6419106.525399597</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6127,7 +6023,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6137,7 +6033,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6151,68 +6047,89 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103768375</v>
+        <v>86334843</v>
       </c>
       <c r="B49" t="n">
-        <v>86320</v>
+        <v>107333</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4398</v>
+        <v>1758</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+          <t>Taraxacum maculigerum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 6, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436391.2907674325</v>
+        <v>436572.0813967428</v>
       </c>
       <c r="R49" t="n">
-        <v>6419116.424034242</v>
+        <v>6419135.34599164</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6234,24 +6151,29 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>F-Hab-0701</t>
+        </is>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6260,28 +6182,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103768170</v>
+        <v>103768145</v>
       </c>
       <c r="B50" t="n">
-        <v>85002</v>
+        <v>86159</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6294,21 +6221,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3295</v>
+        <v>806</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Luktvaxskivling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Corner</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6391,10 +6318,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103768363</v>
+        <v>103769665</v>
       </c>
       <c r="B51" t="n">
-        <v>86117</v>
+        <v>86110</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6403,25 +6330,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>803</v>
+        <v>239221</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Papegojvaxskivling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6432,10 +6359,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436391.2907674325</v>
+        <v>436345.3451666282</v>
       </c>
       <c r="R51" t="n">
-        <v>6419116.424034242</v>
+        <v>6419106.525399597</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6467,7 +6394,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6477,7 +6404,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6504,10 +6431,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103768082</v>
+        <v>103768375</v>
       </c>
       <c r="B52" t="n">
-        <v>86166</v>
+        <v>86320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6516,37 +6443,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>809</v>
+        <v>4398</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6589,7 +6503,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6599,7 +6513,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6626,10 +6540,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103768155</v>
+        <v>103768170</v>
       </c>
       <c r="B53" t="n">
-        <v>86314</v>
+        <v>85002</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6642,19 +6556,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4392</v>
+        <v>3295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Clavulinopsis helvola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6735,7 +6653,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103769675</v>
+        <v>103768363</v>
       </c>
       <c r="B54" t="n">
         <v>86117</v>
@@ -6776,10 +6694,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436345.3451666282</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R54" t="n">
-        <v>6419106.525399597</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6811,7 +6729,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6821,7 +6739,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6848,10 +6766,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103768272</v>
+        <v>103768082</v>
       </c>
       <c r="B55" t="n">
-        <v>85963</v>
+        <v>86166</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6864,35 +6782,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>606</v>
+        <v>809</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mjölrödskivling</t>
+          <t>Praktvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entoloma prunuloides</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436381.4818315752</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R55" t="n">
-        <v>6419102.23161179</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6924,7 +6851,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6934,7 +6861,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6961,10 +6888,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103819472</v>
+        <v>103768155</v>
       </c>
       <c r="B56" t="n">
-        <v>86157</v>
+        <v>86314</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6973,48 +6900,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>805</v>
+        <v>4392</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436397.4421099757</v>
+        <v>436381.4818315752</v>
       </c>
       <c r="R56" t="n">
-        <v>6419101.446833832</v>
+        <v>6419102.23161179</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7038,22 +6955,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7062,22 +6979,367 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>103769675</v>
+      </c>
+      <c r="B57" t="n">
+        <v>86117</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>803</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lutvaxskivling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neohygrocybe nitrata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Pers.) Kovalenko</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>436345.3451666282</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6419106.525399597</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>103768272</v>
+      </c>
+      <c r="B58" t="n">
+        <v>85963</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>606</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mjölrödskivling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Entoloma prunuloides</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Jäboruder, Habo, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>436381.4818315752</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6419102.23161179</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>103819472</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86157</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>805</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Scharlakansvaxskivling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>436397.4421099757</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6419101.446833832</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>Johanne Mossberg</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>Johanne Mossberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,7 +2127,7 @@
         <v>1617733</v>
       </c>
       <c r="B14" t="n">
-        <v>88453</v>
+        <v>88457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>436453</v>
       </c>
       <c r="R14" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2657,7 +2657,7 @@
         <v>1096544</v>
       </c>
       <c r="B19" t="n">
-        <v>88337</v>
+        <v>88341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>436453</v>
       </c>
       <c r="R19" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1190063</v>
+        <v>1248020</v>
       </c>
       <c r="B22" t="n">
-        <v>88394</v>
+        <v>88399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
+          <t>Cuphophyllus virgineus s.lat.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
         <v>436453</v>
       </c>
       <c r="R22" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1248020</v>
+        <v>1221014</v>
       </c>
       <c r="B23" t="n">
-        <v>88395</v>
+        <v>88452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,20 +3081,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4398</v>
+        <v>4394</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3106,7 +3111,7 @@
         <v>436453</v>
       </c>
       <c r="R23" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3133,12 +3138,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,7 +3161,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3172,10 +3176,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1221014</v>
+        <v>1209184</v>
       </c>
       <c r="B24" t="n">
-        <v>88452</v>
+        <v>88406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,23 +3187,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4394</v>
+        <v>4393</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
+          <t>Gliophorus psittacinus s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3278,47 +3278,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1247452</v>
+        <v>4535752</v>
       </c>
       <c r="B25" t="n">
-        <v>88384</v>
+        <v>95590</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4398</v>
+        <v>222112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436453</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R25" t="n">
-        <v>6419121</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,12 +3348,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,71 +3372,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1209184</v>
+        <v>472939</v>
       </c>
       <c r="B26" t="n">
-        <v>88406</v>
+        <v>104540</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4393</v>
+        <v>1174</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Pedicularis sylvatica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436453</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R26" t="n">
-        <v>6419121</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3444,12 +3460,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2008-06-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2008-06-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,75 +3484,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1096336</v>
+        <v>3873115</v>
       </c>
       <c r="B27" t="n">
-        <v>88326</v>
+        <v>103426</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3294</v>
+        <v>221447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Corner</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436453</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R27" t="n">
-        <v>6419121</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,12 +3568,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,31 +3592,25 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4535752</v>
+        <v>4536303</v>
       </c>
       <c r="B28" t="n">
         <v>95590</v>
@@ -3628,10 +3650,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436458.7635083896</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R28" t="n">
-        <v>6419140.861195157</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3658,7 +3680,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3668,7 +3690,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3700,10 +3722,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>472939</v>
+        <v>2366753</v>
       </c>
       <c r="B29" t="n">
-        <v>104540</v>
+        <v>104837</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3712,20 +3734,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3740,13 +3762,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436458.7635083896</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R29" t="n">
-        <v>6419140.861195157</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3770,7 +3792,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3780,7 +3802,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -3812,10 +3834,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3873115</v>
+        <v>481765</v>
       </c>
       <c r="B30" t="n">
-        <v>103426</v>
+        <v>104540</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,37 +3846,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221447</v>
+        <v>1174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>Pedicularis sylvatica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 3, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436459.1625334214</v>
+        <v>436508.1585393944</v>
       </c>
       <c r="R30" t="n">
-        <v>6419098.873399709</v>
+        <v>6419099.690997186</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3876,9 +3911,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>F-Hab-0069</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3888,12 +3928,17 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,11 +3961,15 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4536303</v>
+        <v>4540051</v>
       </c>
       <c r="B31" t="n">
         <v>95590</v>
@@ -3953,20 +4002,29 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436459.1625334214</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R31" t="n">
-        <v>6419098.873399709</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3990,7 +4048,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4000,7 +4058,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4032,7 +4090,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2366753</v>
+        <v>2337603</v>
       </c>
       <c r="B32" t="n">
         <v>104837</v>
@@ -4068,17 +4126,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436535.8438908673</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R32" t="n">
-        <v>6419133.262726188</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4102,7 +4160,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4112,7 +4170,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4132,22 +4190,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>481765</v>
+        <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>104540</v>
+        <v>106756</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,16 +4222,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1174</v>
+        <v>220228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4177,29 +4239,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jäboruder 3, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436508.1585393944</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R33" t="n">
-        <v>6419099.690997186</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4221,14 +4274,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>F-Hab-0069</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4238,17 +4286,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,26 +4306,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Västergötlands flora 2002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4540051</v>
+        <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>95590</v>
+        <v>103426</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4291,50 +4334,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222112</v>
+        <v>221447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436535.8438908673</v>
+        <v>436406.0461207972</v>
       </c>
       <c r="R34" t="n">
-        <v>6419133.262726188</v>
+        <v>6419274.547413215</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,7 +4388,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4368,7 +4398,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4388,22 +4418,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2337603</v>
+        <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>104837</v>
+        <v>104540</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4412,20 +4446,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219955</v>
+        <v>1174</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4436,7 +4470,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4470,7 +4504,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4480,7 +4514,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4505,7 +4539,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4516,10 +4550,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2642441</v>
+        <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>106756</v>
+        <v>95590</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,27 +4566,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220228</v>
+        <v>222112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4586,7 +4620,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4596,7 +4630,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4621,7 +4655,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4632,10 +4666,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3849133</v>
+        <v>467027</v>
       </c>
       <c r="B37" t="n">
-        <v>103426</v>
+        <v>104541</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4644,37 +4678,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221447</v>
+        <v>1174</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Pedicularis sylvatica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436406.0461207972</v>
+        <v>436502.7055573605</v>
       </c>
       <c r="R37" t="n">
-        <v>6419274.547413215</v>
+        <v>6419158.763860945</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4698,7 +4736,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4708,12 +4746,17 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4728,26 +4771,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anna Isaksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Via Anna Isaksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>453603</v>
+        <v>75339585</v>
       </c>
       <c r="B38" t="n">
-        <v>104540</v>
+        <v>108526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4760,16 +4799,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1174</v>
+        <v>220204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4778,16 +4817,20 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436507.2332066745</v>
+        <v>436529</v>
       </c>
       <c r="R38" t="n">
-        <v>6419175.697058928</v>
+        <v>6419163</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -4814,22 +4857,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,75 +4876,90 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Västergötlands flora 2002</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4531256</v>
+        <v>437488</v>
       </c>
       <c r="B39" t="n">
-        <v>95590</v>
+        <v>76591</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222112</v>
+        <v>1591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Knubbig hårjordtunga</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Trichoglossum walteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Berk.) E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436507.2332066745</v>
+        <v>436542.2437137502</v>
       </c>
       <c r="R39" t="n">
-        <v>6419175.697058928</v>
+        <v>6419201.181122187</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4983,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4940,7 +4993,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -4957,29 +5010,31 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>467027</v>
+        <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>104541</v>
+        <v>104838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4988,20 +5043,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5012,17 +5067,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 5, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436502.7055573605</v>
+        <v>436529.3954344561</v>
       </c>
       <c r="R40" t="n">
-        <v>6419158.763860945</v>
+        <v>6419163.123649723</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5044,9 +5099,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>F-Hab-0342</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5056,17 +5116,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,26 +5136,30 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Isaksson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Anna Isaksson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>75339585</v>
+        <v>310069</v>
       </c>
       <c r="B41" t="n">
-        <v>108526</v>
+        <v>86117</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5109,38 +5168,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220204</v>
+        <v>803</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Lutvaxskivling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436529</v>
+        <v>436453.112063889</v>
       </c>
       <c r="R41" t="n">
-        <v>6419163</v>
+        <v>6419120.225843054</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
@@ -5167,17 +5222,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2007-10-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2007-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5186,38 +5246,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Betesmark-häst</t>
-        </is>
-      </c>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>ÅGP inventering</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>437488</v>
+        <v>576272</v>
       </c>
       <c r="B42" t="n">
-        <v>76591</v>
+        <v>107333</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5230,46 +5290,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1591</v>
+        <v>1758</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knubbig hårjordtunga</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Trichoglossum walteri</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk.) E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436542.2437137502</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R42" t="n">
-        <v>6419201.181122187</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5293,7 +5344,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5303,7 +5354,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5320,35 +5371,29 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>75773478</v>
+        <v>576271</v>
       </c>
       <c r="B43" t="n">
-        <v>104838</v>
+        <v>107333</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5357,34 +5402,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219955</v>
+        <v>1758</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäboruder 5, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436529.3954344561</v>
+        <v>436473.7803032578</v>
       </c>
       <c r="R43" t="n">
-        <v>6419163.123649723</v>
+        <v>6419080.573521676</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5409,14 +5454,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>F-Hab-0342</t>
-        </is>
-      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5426,7 +5466,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5434,6 +5474,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5442,30 +5487,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>310069</v>
+        <v>576247</v>
       </c>
       <c r="B44" t="n">
-        <v>86117</v>
+        <v>107333</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5474,41 +5520,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>803</v>
+        <v>1758</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 1, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436453.112063889</v>
+        <v>436519.3450587477</v>
       </c>
       <c r="R44" t="n">
-        <v>6419120.225843054</v>
+        <v>6419100.045175258</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5530,9 +5576,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>F-Hab-0065</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5542,7 +5593,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5550,6 +5601,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Mycket blad bör kollas nästa år</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5564,73 +5620,76 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr"/>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>ÅGP inventering</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>576272</v>
+        <v>86334010</v>
       </c>
       <c r="B45" t="n">
-        <v>107333</v>
+        <v>106757</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1758</v>
+        <v>220228</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436459.1625334214</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R45" t="n">
-        <v>6419098.873399709</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5654,7 +5713,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5664,7 +5723,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5678,8 +5737,14 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5696,7 +5761,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>576271</v>
+        <v>86334843</v>
       </c>
       <c r="B46" t="n">
         <v>107333</v>
@@ -5729,17 +5794,29 @@
           <t>H. Lindb.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 6, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436473.7803032578</v>
+        <v>436572.0813967428</v>
       </c>
       <c r="R46" t="n">
-        <v>6419080.573521676</v>
+        <v>6419135.34599164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5764,9 +5841,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>F-Hab-0701</t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5776,7 +5858,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -5784,87 +5866,83 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>576247</v>
+        <v>103768145</v>
       </c>
       <c r="B47" t="n">
-        <v>107333</v>
+        <v>86159</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1758</v>
+        <v>806</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Luktvaxskivling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäboruder 1, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436519.3450587477</v>
+        <v>436381.4818315752</v>
       </c>
       <c r="R47" t="n">
-        <v>6419100.045175258</v>
+        <v>6419102.23161179</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5886,34 +5964,24 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>F-Hab-0065</t>
-        </is>
-      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Mycket blad bör kollas nästa år</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5924,35 +5992,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>86334010</v>
+        <v>103769665</v>
       </c>
       <c r="B48" t="n">
-        <v>106757</v>
+        <v>86110</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5961,45 +6020,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220228</v>
+        <v>239221</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Papegojvaxskivling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436458.7635083896</v>
+        <v>436345.3451666282</v>
       </c>
       <c r="R48" t="n">
-        <v>6419140.861195157</v>
+        <v>6419106.525399597</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6023,7 +6079,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6033,7 +6089,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6047,89 +6103,68 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>86334843</v>
+        <v>103768375</v>
       </c>
       <c r="B49" t="n">
-        <v>107333</v>
+        <v>86320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1758</v>
+        <v>4398</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>H. Lindb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäboruder 6, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436572.0813967428</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R49" t="n">
-        <v>6419135.34599164</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6151,29 +6186,24 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>F-Hab-0701</t>
-        </is>
-      </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6182,33 +6212,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103768145</v>
+        <v>103768170</v>
       </c>
       <c r="B50" t="n">
-        <v>86159</v>
+        <v>85002</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6221,21 +6246,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>806</v>
+        <v>3295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>(Pers.:Fr.) Corner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6318,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103769665</v>
+        <v>103768363</v>
       </c>
       <c r="B51" t="n">
-        <v>86110</v>
+        <v>86117</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6330,25 +6355,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>239221</v>
+        <v>803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling</t>
+          <t>Lutvaxskivling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Herink</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6359,10 +6384,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436345.3451666282</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R51" t="n">
-        <v>6419106.525399597</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6394,7 +6419,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6404,7 +6429,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6431,10 +6456,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103768375</v>
+        <v>103768082</v>
       </c>
       <c r="B52" t="n">
-        <v>86320</v>
+        <v>86166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6443,24 +6468,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4398</v>
+        <v>809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Praktvaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>Hygrocybe splendidissima</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6503,7 +6541,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6513,7 +6551,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6540,10 +6578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103768170</v>
+        <v>103768155</v>
       </c>
       <c r="B53" t="n">
-        <v>85002</v>
+        <v>86314</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6556,23 +6594,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3295</v>
+        <v>4392</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Corner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6653,7 +6687,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103768363</v>
+        <v>103769675</v>
       </c>
       <c r="B54" t="n">
         <v>86117</v>
@@ -6694,10 +6728,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436391.2907674325</v>
+        <v>436345.3451666282</v>
       </c>
       <c r="R54" t="n">
-        <v>6419116.424034242</v>
+        <v>6419106.525399597</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6729,7 +6763,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6739,7 +6773,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6766,10 +6800,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103768082</v>
+        <v>103768272</v>
       </c>
       <c r="B55" t="n">
-        <v>86166</v>
+        <v>85963</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6782,44 +6816,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>809</v>
+        <v>606</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Mjölrödskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
+          <t>Entoloma prunuloides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436391.2907674325</v>
+        <v>436381.4818315752</v>
       </c>
       <c r="R55" t="n">
-        <v>6419116.424034242</v>
+        <v>6419102.23161179</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6851,7 +6876,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6861,7 +6886,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6888,10 +6913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103768155</v>
+        <v>103819472</v>
       </c>
       <c r="B56" t="n">
-        <v>86314</v>
+        <v>86157</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6900,38 +6925,48 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4392</v>
+        <v>805</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436381.4818315752</v>
+        <v>436397.4421099757</v>
       </c>
       <c r="R56" t="n">
-        <v>6419102.23161179</v>
+        <v>6419101.446833832</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6955,22 +6990,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6979,367 +7014,22 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Johanne Mossberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Johanne Mossberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>103769675</v>
-      </c>
-      <c r="B57" t="n">
-        <v>86117</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>803</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Lutvaxskivling</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Neohygrocybe nitrata</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Pers.) Kovalenko</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Jäboruder, Vg</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>436345.3451666282</v>
-      </c>
-      <c r="R57" t="n">
-        <v>6419106.525399597</v>
-      </c>
-      <c r="S57" t="n">
-        <v>25</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>103768272</v>
-      </c>
-      <c r="B58" t="n">
-        <v>85963</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>606</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Mjölrödskivling</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Entoloma prunuloides</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Jäboruder, Habo, Vg</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>436381.4818315752</v>
-      </c>
-      <c r="R58" t="n">
-        <v>6419102.23161179</v>
-      </c>
-      <c r="S58" t="n">
-        <v>25</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>103819472</v>
-      </c>
-      <c r="B59" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>805</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Scharlakansvaxskivling</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Jäboruder, Vg</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>436397.4421099757</v>
-      </c>
-      <c r="R59" t="n">
-        <v>6419101.446833832</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Johanne Mossberg</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Johanne Mossberg</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2164,7 +2164,7 @@
         <v>436453</v>
       </c>
       <c r="R14" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2694,7 +2694,7 @@
         <v>436453</v>
       </c>
       <c r="R19" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1248020</v>
+        <v>1190063</v>
       </c>
       <c r="B22" t="n">
-        <v>88399</v>
+        <v>88398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4398</v>
+        <v>4392</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
+          <t>Cuphophyllus pratensis s.lat.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
         <v>436453</v>
       </c>
       <c r="R22" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1221014</v>
+        <v>1248020</v>
       </c>
       <c r="B23" t="n">
-        <v>88452</v>
+        <v>88399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,25 +3081,20 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4394</v>
+        <v>4398</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3111,7 +3106,7 @@
         <v>436453</v>
       </c>
       <c r="R23" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3138,12 +3133,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2007-10-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2007-10-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,6 +3156,7 @@
           <t>Betesmark</t>
         </is>
       </c>
+      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3176,10 +3172,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1209184</v>
+        <v>1221014</v>
       </c>
       <c r="B24" t="n">
-        <v>88406</v>
+        <v>88452</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,19 +3183,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4393</v>
+        <v>4394</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3278,53 +3278,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4535752</v>
+        <v>1247452</v>
       </c>
       <c r="B25" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88384</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222112</v>
+        <v>4398</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R25" t="n">
-        <v>6419140.861195157</v>
+        <v>6419121</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3348,22 +3342,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,71 +3356,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>472939</v>
+        <v>1209184</v>
       </c>
       <c r="B26" t="n">
-        <v>104540</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88406</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1174</v>
+        <v>4393</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gliophorus psittacinus s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R26" t="n">
-        <v>6419140.861195157</v>
+        <v>6419121</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,22 +3444,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,67 +3458,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3873115</v>
+        <v>1096336</v>
       </c>
       <c r="B27" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221447</v>
+        <v>3294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436459.1625334214</v>
+        <v>436453</v>
       </c>
       <c r="R27" t="n">
-        <v>6419098.873399709</v>
+        <v>6419121</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,22 +3550,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,25 +3564,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4536303</v>
+        <v>4535752</v>
       </c>
       <c r="B28" t="n">
         <v>95590</v>
@@ -3650,10 +3628,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436459.1625334214</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R28" t="n">
-        <v>6419098.873399709</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3680,7 +3658,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3690,7 +3668,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3722,10 +3700,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2366753</v>
+        <v>472939</v>
       </c>
       <c r="B29" t="n">
-        <v>104837</v>
+        <v>104540</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3734,20 +3712,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219955</v>
+        <v>1174</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3762,13 +3740,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436535.8438908673</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R29" t="n">
-        <v>6419133.262726188</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,7 +3770,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3802,7 +3780,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -3834,10 +3812,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>481765</v>
+        <v>3873115</v>
       </c>
       <c r="B30" t="n">
-        <v>104540</v>
+        <v>103426</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3846,50 +3824,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1174</v>
+        <v>221447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäboruder 3, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436508.1585393944</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R30" t="n">
-        <v>6419099.690997186</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,14 +3876,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>F-Hab-0069</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3928,17 +3888,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3961,15 +3916,11 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4540051</v>
+        <v>4536303</v>
       </c>
       <c r="B31" t="n">
         <v>95590</v>
@@ -4002,29 +3953,20 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436535.8438908673</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R31" t="n">
-        <v>6419133.262726188</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4048,7 +3990,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4058,7 +4000,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4090,7 +4032,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2337603</v>
+        <v>2366753</v>
       </c>
       <c r="B32" t="n">
         <v>104837</v>
@@ -4126,17 +4068,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436507.2332066745</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R32" t="n">
-        <v>6419175.697058928</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4160,7 +4102,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4170,7 +4112,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4190,26 +4132,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2642441</v>
+        <v>481765</v>
       </c>
       <c r="B33" t="n">
-        <v>106756</v>
+        <v>104540</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4222,16 +4160,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220228</v>
+        <v>1174</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4239,20 +4177,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder 3, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436507.2332066745</v>
+        <v>436508.1585393944</v>
       </c>
       <c r="R33" t="n">
-        <v>6419175.697058928</v>
+        <v>6419099.690997186</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4274,9 +4221,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>F-Hab-0069</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4286,12 +4238,17 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4306,26 +4263,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Västergötlands flora 2002</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3849133</v>
+        <v>4540051</v>
       </c>
       <c r="B34" t="n">
-        <v>103426</v>
+        <v>95590</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4334,37 +4291,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221447</v>
+        <v>222112</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436406.0461207972</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R34" t="n">
-        <v>6419274.547413215</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4388,7 +4358,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4398,7 +4368,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4418,26 +4388,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>453603</v>
+        <v>2337603</v>
       </c>
       <c r="B35" t="n">
-        <v>104540</v>
+        <v>104837</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,20 +4412,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4470,7 +4436,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4504,7 +4470,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4514,7 +4480,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4539,7 +4505,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4550,10 +4516,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4531256</v>
+        <v>2642441</v>
       </c>
       <c r="B36" t="n">
-        <v>95590</v>
+        <v>106756</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4566,27 +4532,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222112</v>
+        <v>220228</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4620,7 +4586,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4630,7 +4596,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4655,7 +4621,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4666,10 +4632,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>467027</v>
+        <v>3849133</v>
       </c>
       <c r="B37" t="n">
-        <v>104541</v>
+        <v>103426</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4678,41 +4644,37 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1174</v>
+        <v>221447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436502.7055573605</v>
+        <v>436406.0461207972</v>
       </c>
       <c r="R37" t="n">
-        <v>6419158.763860945</v>
+        <v>6419274.547413215</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4736,7 +4698,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4746,17 +4708,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,22 +4728,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Isaksson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Anna Isaksson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>75339585</v>
+        <v>453603</v>
       </c>
       <c r="B38" t="n">
-        <v>108526</v>
+        <v>104540</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4799,16 +4760,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220204</v>
+        <v>1174</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4817,20 +4778,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436529</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R38" t="n">
-        <v>6419163</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -4857,17 +4814,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>1997-06-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>1997-06-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4876,90 +4838,75 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Västergötlands flora 2002</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>437488</v>
+        <v>4531256</v>
       </c>
       <c r="B39" t="n">
-        <v>76591</v>
+        <v>95590</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1591</v>
+        <v>222112</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knubbig hårjordtunga</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichoglossum walteri</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk.) E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436542.2437137502</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R39" t="n">
-        <v>6419201.181122187</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4983,7 +4930,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4993,7 +4940,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5010,31 +4957,29 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Gösta Börjeson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>75773478</v>
+        <v>467027</v>
       </c>
       <c r="B40" t="n">
-        <v>104838</v>
+        <v>104541</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5043,20 +4988,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219955</v>
+        <v>1174</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5067,17 +5012,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäboruder 5, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436529.3954344561</v>
+        <v>436502.7055573605</v>
       </c>
       <c r="R40" t="n">
-        <v>6419163.123649723</v>
+        <v>6419158.763860945</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5099,14 +5044,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>F-Hab-0342</t>
-        </is>
-      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5116,12 +5056,17 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5136,30 +5081,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anna Isaksson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Via Anna Isaksson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>310069</v>
+        <v>75339585</v>
       </c>
       <c r="B41" t="n">
-        <v>86117</v>
+        <v>108526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5168,34 +5109,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>803</v>
+        <v>220204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436453.112063889</v>
+        <v>436529</v>
       </c>
       <c r="R41" t="n">
-        <v>6419120.225843054</v>
+        <v>6419163</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
@@ -5222,22 +5167,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5246,38 +5186,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr"/>
+          <t>Betesmark-häst</t>
+        </is>
+      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>ÅGP inventering</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>576272</v>
+        <v>437488</v>
       </c>
       <c r="B42" t="n">
-        <v>107333</v>
+        <v>76591</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5290,37 +5230,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1758</v>
+        <v>1591</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Knubbig hårjordtunga</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Trichoglossum walteri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Berk.) E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436459.1625334214</v>
+        <v>436542.2437137502</v>
       </c>
       <c r="R42" t="n">
-        <v>6419098.873399709</v>
+        <v>6419201.181122187</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5344,7 +5293,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5354,7 +5303,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5371,29 +5320,35 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>576271</v>
+        <v>75773478</v>
       </c>
       <c r="B43" t="n">
-        <v>107333</v>
+        <v>104838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5402,34 +5357,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1758</v>
+        <v>219955</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 5, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436473.7803032578</v>
+        <v>436529.3954344561</v>
       </c>
       <c r="R43" t="n">
-        <v>6419080.573521676</v>
+        <v>6419163.123649723</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5454,9 +5409,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>F-Hab-0342</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5466,7 +5426,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5474,11 +5434,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5487,31 +5442,30 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>576247</v>
+        <v>310069</v>
       </c>
       <c r="B44" t="n">
-        <v>107333</v>
+        <v>86117</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5520,41 +5474,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1758</v>
+        <v>803</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Lutvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäboruder 1, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436519.3450587477</v>
+        <v>436453.112063889</v>
       </c>
       <c r="R44" t="n">
-        <v>6419100.045175258</v>
+        <v>6419120.225843054</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5576,14 +5530,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>F-Hab-0065</t>
-        </is>
-      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5593,7 +5542,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5601,11 +5550,6 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Mycket blad bör kollas nästa år</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5620,76 +5564,73 @@
           <t>Betesmark</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr"/>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>ÅGP inventering</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>86334010</v>
+        <v>576272</v>
       </c>
       <c r="B45" t="n">
-        <v>106757</v>
+        <v>107333</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220228</v>
+        <v>1758</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436458.7635083896</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R45" t="n">
-        <v>6419140.861195157</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5713,7 +5654,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5723,7 +5664,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5737,14 +5678,8 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5761,7 +5696,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>86334843</v>
+        <v>576271</v>
       </c>
       <c r="B46" t="n">
         <v>107333</v>
@@ -5794,29 +5729,17 @@
           <t>H. Lindb.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäboruder 6, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436572.0813967428</v>
+        <v>436473.7803032578</v>
       </c>
       <c r="R46" t="n">
-        <v>6419135.34599164</v>
+        <v>6419080.573521676</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5841,14 +5764,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>F-Hab-0701</t>
-        </is>
-      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5858,7 +5776,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -5866,83 +5784,87 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103768145</v>
+        <v>576247</v>
       </c>
       <c r="B47" t="n">
-        <v>86159</v>
+        <v>107333</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>806</v>
+        <v>1758</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder 1, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436381.4818315752</v>
+        <v>436519.3450587477</v>
       </c>
       <c r="R47" t="n">
-        <v>6419102.23161179</v>
+        <v>6419100.045175258</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5964,24 +5886,34 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>F-Hab-0065</t>
+        </is>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mycket blad bör kollas nästa år</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5992,26 +5924,35 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103769665</v>
+        <v>86334010</v>
       </c>
       <c r="B48" t="n">
-        <v>86110</v>
+        <v>106757</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6020,42 +5961,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>239221</v>
+        <v>220228</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schaeff.) Herink</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436345.3451666282</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R48" t="n">
-        <v>6419106.525399597</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6079,7 +6023,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6089,7 +6033,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6103,68 +6047,89 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103768375</v>
+        <v>86334843</v>
       </c>
       <c r="B49" t="n">
-        <v>86320</v>
+        <v>107333</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4398</v>
+        <v>1758</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+          <t>Taraxacum maculigerum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 6, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436391.2907674325</v>
+        <v>436572.0813967428</v>
       </c>
       <c r="R49" t="n">
-        <v>6419116.424034242</v>
+        <v>6419135.34599164</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6186,24 +6151,29 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>F-Hab-0701</t>
+        </is>
+      </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6212,28 +6182,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103768170</v>
+        <v>103768145</v>
       </c>
       <c r="B50" t="n">
-        <v>85002</v>
+        <v>86159</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6246,21 +6221,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3295</v>
+        <v>806</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Luktvaxskivling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Corner</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6343,10 +6318,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103768363</v>
+        <v>103769665</v>
       </c>
       <c r="B51" t="n">
-        <v>86117</v>
+        <v>86110</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6355,25 +6330,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>803</v>
+        <v>239221</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Papegojvaxskivling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6384,10 +6359,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436391.2907674325</v>
+        <v>436345.3451666282</v>
       </c>
       <c r="R51" t="n">
-        <v>6419116.424034242</v>
+        <v>6419106.525399597</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6419,7 +6394,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6429,7 +6404,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6456,10 +6431,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103768082</v>
+        <v>103768375</v>
       </c>
       <c r="B52" t="n">
-        <v>86166</v>
+        <v>86320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6468,37 +6443,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>809</v>
+        <v>4398</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6541,7 +6503,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6551,7 +6513,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6578,10 +6540,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103768155</v>
+        <v>103768170</v>
       </c>
       <c r="B53" t="n">
-        <v>86314</v>
+        <v>85002</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6594,19 +6556,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4392</v>
+        <v>3295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Clavulinopsis helvola</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6687,7 +6653,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103769675</v>
+        <v>103768363</v>
       </c>
       <c r="B54" t="n">
         <v>86117</v>
@@ -6728,10 +6694,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436345.3451666282</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R54" t="n">
-        <v>6419106.525399597</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6763,7 +6729,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6773,7 +6739,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6800,10 +6766,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103768272</v>
+        <v>103768082</v>
       </c>
       <c r="B55" t="n">
-        <v>85963</v>
+        <v>86166</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6816,35 +6782,44 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>606</v>
+        <v>809</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mjölrödskivling</t>
+          <t>Praktvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entoloma prunuloides</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436381.4818315752</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R55" t="n">
-        <v>6419102.23161179</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6876,7 +6851,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6886,7 +6861,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6913,10 +6888,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103819472</v>
+        <v>103768155</v>
       </c>
       <c r="B56" t="n">
-        <v>86157</v>
+        <v>86314</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6925,48 +6900,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>805</v>
+        <v>4392</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436397.4421099757</v>
+        <v>436381.4818315752</v>
       </c>
       <c r="R56" t="n">
-        <v>6419101.446833832</v>
+        <v>6419102.23161179</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6990,22 +6955,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7014,22 +6979,367 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>103769675</v>
+      </c>
+      <c r="B57" t="n">
+        <v>86117</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>803</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Lutvaxskivling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neohygrocybe nitrata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Pers.) Kovalenko</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>436345.3451666282</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6419106.525399597</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>103768272</v>
+      </c>
+      <c r="B58" t="n">
+        <v>85963</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>606</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Mjölrödskivling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Entoloma prunuloides</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Jäboruder, Habo, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>436381.4818315752</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6419102.23161179</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>103819472</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86157</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>805</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Scharlakansvaxskivling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>436397.4421099757</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6419101.446833832</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>Johanne Mossberg</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>Johanne Mossberg</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2694,7 +2694,7 @@
         <v>436453</v>
       </c>
       <c r="R19" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -2968,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1190063</v>
+        <v>1248020</v>
       </c>
       <c r="B22" t="n">
-        <v>88398</v>
+        <v>88399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,16 +2979,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
+          <t>Cuphophyllus virgineus s.lat.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -3004,7 +3004,7 @@
         <v>436453</v>
       </c>
       <c r="R22" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1248020</v>
+        <v>1221014</v>
       </c>
       <c r="B23" t="n">
-        <v>88399</v>
+        <v>88452</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,20 +3081,25 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4398</v>
+        <v>4394</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Hygrocybe reidii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kühner</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3106,7 +3111,7 @@
         <v>436453</v>
       </c>
       <c r="R23" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3133,12 +3138,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,7 +3161,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr"/>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3172,10 +3176,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1221014</v>
+        <v>1209184</v>
       </c>
       <c r="B24" t="n">
-        <v>88452</v>
+        <v>88406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3183,23 +3187,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4394</v>
+        <v>4393</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kühner</t>
-        </is>
-      </c>
+          <t>Gliophorus psittacinus s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3278,47 +3278,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1247452</v>
+        <v>4535752</v>
       </c>
       <c r="B25" t="n">
-        <v>88384</v>
+        <v>95590</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4398</v>
+        <v>222112</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436453</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R25" t="n">
-        <v>6419121</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3342,12 +3348,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,71 +3372,71 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1209184</v>
+        <v>472939</v>
       </c>
       <c r="B26" t="n">
-        <v>88406</v>
+        <v>104540</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4393</v>
+        <v>1174</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Pedicularis sylvatica</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436453</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R26" t="n">
-        <v>6419121</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3444,12 +3460,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2008-06-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2008-06-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3458,75 +3484,67 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1096336</v>
+        <v>3873115</v>
       </c>
       <c r="B27" t="n">
-        <v>88326</v>
+        <v>103426</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3294</v>
+        <v>221447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Corner</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436453</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R27" t="n">
-        <v>6419121</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S27" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,12 +3568,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3564,31 +3592,25 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4535752</v>
+        <v>4536303</v>
       </c>
       <c r="B28" t="n">
         <v>95590</v>
@@ -3628,10 +3650,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436458.7635083896</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R28" t="n">
-        <v>6419140.861195157</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S28" t="n">
         <v>50</v>
@@ -3658,7 +3680,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3668,7 +3690,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3700,10 +3722,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>472939</v>
+        <v>2366753</v>
       </c>
       <c r="B29" t="n">
-        <v>104540</v>
+        <v>104837</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3712,20 +3734,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3740,13 +3762,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436458.7635083896</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R29" t="n">
-        <v>6419140.861195157</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3770,7 +3792,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3780,7 +3802,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -3812,10 +3834,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3873115</v>
+        <v>481765</v>
       </c>
       <c r="B30" t="n">
-        <v>103426</v>
+        <v>104540</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3824,37 +3846,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221447</v>
+        <v>1174</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>Pedicularis sylvatica</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 3, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436459.1625334214</v>
+        <v>436508.1585393944</v>
       </c>
       <c r="R30" t="n">
-        <v>6419098.873399709</v>
+        <v>6419099.690997186</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3876,9 +3911,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>F-Hab-0069</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3888,12 +3928,17 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3916,11 +3961,15 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4536303</v>
+        <v>4540051</v>
       </c>
       <c r="B31" t="n">
         <v>95590</v>
@@ -3953,20 +4002,29 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436459.1625334214</v>
+        <v>436535.8438908673</v>
       </c>
       <c r="R31" t="n">
-        <v>6419098.873399709</v>
+        <v>6419133.262726188</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3990,7 +4048,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4000,7 +4058,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4032,7 +4090,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2366753</v>
+        <v>2337603</v>
       </c>
       <c r="B32" t="n">
         <v>104837</v>
@@ -4068,17 +4126,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436535.8438908673</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R32" t="n">
-        <v>6419133.262726188</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4102,7 +4160,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4112,7 +4170,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4132,22 +4190,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>481765</v>
+        <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>104540</v>
+        <v>106756</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4160,16 +4222,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1174</v>
+        <v>220228</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4177,29 +4239,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Jäboruder 3, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436508.1585393944</v>
+        <v>436507.2332066745</v>
       </c>
       <c r="R33" t="n">
-        <v>6419099.690997186</v>
+        <v>6419175.697058928</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4221,14 +4274,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>F-Hab-0069</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4238,17 +4286,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Kanske fler, enormt hårt bete</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,26 +4306,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Västergötlands flora 2002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4540051</v>
+        <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>95590</v>
+        <v>103426</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4291,50 +4334,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222112</v>
+        <v>221447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436535.8438908673</v>
+        <v>436406.0461207972</v>
       </c>
       <c r="R34" t="n">
-        <v>6419133.262726188</v>
+        <v>6419274.547413215</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,7 +4388,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4368,7 +4398,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -4388,22 +4418,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2337603</v>
+        <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>104837</v>
+        <v>104540</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4412,20 +4446,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219955</v>
+        <v>1174</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4436,7 +4470,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4470,7 +4504,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4480,7 +4514,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -4505,7 +4539,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4516,10 +4550,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2642441</v>
+        <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>106756</v>
+        <v>95590</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4532,27 +4566,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220228</v>
+        <v>222112</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -4586,7 +4620,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4596,7 +4630,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -4621,7 +4655,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Gösta Börjeson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4632,10 +4666,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3849133</v>
+        <v>467027</v>
       </c>
       <c r="B37" t="n">
-        <v>103426</v>
+        <v>104541</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4644,37 +4678,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221447</v>
+        <v>1174</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Pedicularis sylvatica</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436406.0461207972</v>
+        <v>436502.7055573605</v>
       </c>
       <c r="R37" t="n">
-        <v>6419274.547413215</v>
+        <v>6419158.763860945</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4698,7 +4736,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4708,12 +4746,17 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4728,26 +4771,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anna Isaksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Via Anna Isaksson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>453603</v>
+        <v>75339585</v>
       </c>
       <c r="B38" t="n">
-        <v>104540</v>
+        <v>108526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4760,16 +4799,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1174</v>
+        <v>220204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4778,16 +4817,20 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436507.2332066745</v>
+        <v>436529</v>
       </c>
       <c r="R38" t="n">
-        <v>6419175.697058928</v>
+        <v>6419163</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -4814,22 +4857,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,75 +4876,90 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Västergötlands flora 2002</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4531256</v>
+        <v>437488</v>
       </c>
       <c r="B39" t="n">
-        <v>95590</v>
+        <v>76591</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222112</v>
+        <v>1591</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Knubbig hårjordtunga</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Trichoglossum walteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Berk.) E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436507.2332066745</v>
+        <v>436542.2437137502</v>
       </c>
       <c r="R39" t="n">
-        <v>6419175.697058928</v>
+        <v>6419201.181122187</v>
       </c>
       <c r="S39" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4930,7 +4983,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4940,7 +4993,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -4957,29 +5010,31 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>467027</v>
+        <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>104541</v>
+        <v>104838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4988,20 +5043,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5012,17 +5067,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 5, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436502.7055573605</v>
+        <v>436529.3954344561</v>
       </c>
       <c r="R40" t="n">
-        <v>6419158.763860945</v>
+        <v>6419163.123649723</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5044,9 +5099,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>F-Hab-0342</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5056,17 +5116,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5081,26 +5136,30 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna Isaksson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Anna Isaksson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>75339585</v>
+        <v>310069</v>
       </c>
       <c r="B41" t="n">
-        <v>108526</v>
+        <v>86117</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5109,38 +5168,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220204</v>
+        <v>803</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Lutvaxskivling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436529</v>
+        <v>436453.112063889</v>
       </c>
       <c r="R41" t="n">
-        <v>6419163</v>
+        <v>6419120.225843054</v>
       </c>
       <c r="S41" t="n">
         <v>100</v>
@@ -5167,17 +5222,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2007-10-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2007-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5186,38 +5246,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Betesmark-häst</t>
-        </is>
-      </c>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr"/>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>ÅGP inventering</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>437488</v>
+        <v>576272</v>
       </c>
       <c r="B42" t="n">
-        <v>76591</v>
+        <v>107333</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5230,46 +5290,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1591</v>
+        <v>1758</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knubbig hårjordtunga</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Trichoglossum walteri</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk.) E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436542.2437137502</v>
+        <v>436459.1625334214</v>
       </c>
       <c r="R42" t="n">
-        <v>6419201.181122187</v>
+        <v>6419098.873399709</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5293,7 +5344,7 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5303,7 +5354,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5320,35 +5371,29 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr"/>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>75773478</v>
+        <v>576271</v>
       </c>
       <c r="B43" t="n">
-        <v>104838</v>
+        <v>107333</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5357,34 +5402,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219955</v>
+        <v>1758</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäboruder 5, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436529.3954344561</v>
+        <v>436473.7803032578</v>
       </c>
       <c r="R43" t="n">
-        <v>6419163.123649723</v>
+        <v>6419080.573521676</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5409,14 +5454,9 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>F-Hab-0342</t>
-        </is>
-      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
@@ -5426,7 +5466,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
@@ -5434,6 +5474,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5442,30 +5487,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>310069</v>
+        <v>576247</v>
       </c>
       <c r="B44" t="n">
-        <v>86117</v>
+        <v>107333</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5474,41 +5520,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>803</v>
+        <v>1758</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 1, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436453.112063889</v>
+        <v>436519.3450587477</v>
       </c>
       <c r="R44" t="n">
-        <v>6419120.225843054</v>
+        <v>6419100.045175258</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5530,9 +5576,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>F-Hab-0065</t>
+        </is>
+      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
@@ -5542,7 +5593,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -5550,6 +5601,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Mycket blad bör kollas nästa år</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5564,73 +5620,76 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr"/>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>ÅGP inventering</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>576272</v>
+        <v>86334010</v>
       </c>
       <c r="B45" t="n">
-        <v>107333</v>
+        <v>106757</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1758</v>
+        <v>220228</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436459.1625334214</v>
+        <v>436458.7635083896</v>
       </c>
       <c r="R45" t="n">
-        <v>6419098.873399709</v>
+        <v>6419140.861195157</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5654,7 +5713,7 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
@@ -5664,7 +5723,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5678,8 +5737,14 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5696,7 +5761,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>576271</v>
+        <v>86334843</v>
       </c>
       <c r="B46" t="n">
         <v>107333</v>
@@ -5729,17 +5794,29 @@
           <t>H. Lindb.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 6, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436473.7803032578</v>
+        <v>436572.0813967428</v>
       </c>
       <c r="R46" t="n">
-        <v>6419080.573521676</v>
+        <v>6419135.34599164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5764,9 +5841,14 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>F-Hab-0701</t>
+        </is>
+      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -5776,7 +5858,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -5784,87 +5866,83 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>576247</v>
+        <v>103768145</v>
       </c>
       <c r="B47" t="n">
-        <v>107333</v>
+        <v>86159</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1758</v>
+        <v>806</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Luktvaxskivling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäboruder 1, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436519.3450587477</v>
+        <v>436381.4818315752</v>
       </c>
       <c r="R47" t="n">
-        <v>6419100.045175258</v>
+        <v>6419102.23161179</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5886,34 +5964,24 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>F-Hab-0065</t>
-        </is>
-      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Mycket blad bör kollas nästa år</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5924,35 +5992,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>86334010</v>
+        <v>103769665</v>
       </c>
       <c r="B48" t="n">
-        <v>106757</v>
+        <v>86110</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5961,45 +6020,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220228</v>
+        <v>239221</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Papegojvaxskivling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436458.7635083896</v>
+        <v>436345.3451666282</v>
       </c>
       <c r="R48" t="n">
-        <v>6419140.861195157</v>
+        <v>6419106.525399597</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6023,7 +6079,7 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6033,7 +6089,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
@@ -6047,89 +6103,68 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>86334843</v>
+        <v>103768375</v>
       </c>
       <c r="B49" t="n">
-        <v>107333</v>
+        <v>86320</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1758</v>
+        <v>4398</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Vit vaxskivling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>H. Lindb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Jäboruder 6, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436572.0813967428</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R49" t="n">
-        <v>6419135.34599164</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6151,29 +6186,24 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>F-Hab-0701</t>
-        </is>
-      </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6182,33 +6212,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103768145</v>
+        <v>103768170</v>
       </c>
       <c r="B50" t="n">
-        <v>86159</v>
+        <v>85002</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6221,21 +6246,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>806</v>
+        <v>3295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Kühner) Singer</t>
+          <t>(Pers.:Fr.) Corner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6318,10 +6343,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103769665</v>
+        <v>103768363</v>
       </c>
       <c r="B51" t="n">
-        <v>86110</v>
+        <v>86117</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6330,25 +6355,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>239221</v>
+        <v>803</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling</t>
+          <t>Lutvaxskivling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Herink</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6359,10 +6384,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436345.3451666282</v>
+        <v>436391.2907674325</v>
       </c>
       <c r="R51" t="n">
-        <v>6419106.525399597</v>
+        <v>6419116.424034242</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6394,7 +6419,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6404,7 +6429,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6431,10 +6456,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103768375</v>
+        <v>103768082</v>
       </c>
       <c r="B52" t="n">
-        <v>86320</v>
+        <v>86166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6443,24 +6468,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4398</v>
+        <v>809</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Praktvaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>Hygrocybe splendidissima</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6503,7 +6541,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6513,7 +6551,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6540,10 +6578,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103768170</v>
+        <v>103768155</v>
       </c>
       <c r="B53" t="n">
-        <v>85002</v>
+        <v>86314</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6556,23 +6594,19 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3295</v>
+        <v>4392</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Ängsvaxskivling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Corner</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6653,7 +6687,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103768363</v>
+        <v>103769675</v>
       </c>
       <c r="B54" t="n">
         <v>86117</v>
@@ -6694,10 +6728,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436391.2907674325</v>
+        <v>436345.3451666282</v>
       </c>
       <c r="R54" t="n">
-        <v>6419116.424034242</v>
+        <v>6419106.525399597</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6729,7 +6763,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6739,7 +6773,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6766,10 +6800,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103768082</v>
+        <v>103768272</v>
       </c>
       <c r="B55" t="n">
-        <v>86166</v>
+        <v>85963</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6782,44 +6816,35 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>809</v>
+        <v>606</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Mjölrödskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
+          <t>Entoloma prunuloides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436391.2907674325</v>
+        <v>436381.4818315752</v>
       </c>
       <c r="R55" t="n">
-        <v>6419116.424034242</v>
+        <v>6419102.23161179</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6851,7 +6876,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6861,7 +6886,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6888,10 +6913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103768155</v>
+        <v>103819472</v>
       </c>
       <c r="B56" t="n">
-        <v>86314</v>
+        <v>86157</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6900,38 +6925,48 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4392</v>
+        <v>805</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Scharlakansvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436381.4818315752</v>
+        <v>436397.4421099757</v>
       </c>
       <c r="R56" t="n">
-        <v>6419102.23161179</v>
+        <v>6419101.446833832</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6955,22 +6990,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6979,367 +7014,22 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Johanne Mossberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Johanne Mossberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>103769675</v>
-      </c>
-      <c r="B57" t="n">
-        <v>86117</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>803</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Lutvaxskivling</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Neohygrocybe nitrata</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Pers.) Kovalenko</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Jäboruder, Vg</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>436345.3451666282</v>
-      </c>
-      <c r="R57" t="n">
-        <v>6419106.525399597</v>
-      </c>
-      <c r="S57" t="n">
-        <v>25</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>103768272</v>
-      </c>
-      <c r="B58" t="n">
-        <v>85963</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>606</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Mjölrödskivling</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Entoloma prunuloides</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Jäboruder, Habo, Vg</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>436381.4818315752</v>
-      </c>
-      <c r="R58" t="n">
-        <v>6419102.23161179</v>
-      </c>
-      <c r="S58" t="n">
-        <v>25</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>103819472</v>
-      </c>
-      <c r="B59" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>805</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Scharlakansvaxskivling</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Jäboruder, Vg</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>436397.4421099757</v>
-      </c>
-      <c r="R59" t="n">
-        <v>6419101.446833832</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Habo</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Johanne Mossberg</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Johanne Mossberg</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -2127,7 +2127,7 @@
         <v>1617733</v>
       </c>
       <c r="B14" t="n">
-        <v>88457</v>
+        <v>88460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>436453</v>
       </c>
       <c r="R14" t="n">
-        <v>6419120</v>
+        <v>6419121</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2657,7 +2657,7 @@
         <v>1096544</v>
       </c>
       <c r="B19" t="n">
-        <v>88341</v>
+        <v>88344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>1248020</v>
       </c>
       <c r="B22" t="n">
-        <v>88399</v>
+        <v>88402</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,12 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>104837</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107248</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4130,10 +4125,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436507.2332066745</v>
+        <v>436507</v>
       </c>
       <c r="R32" t="n">
-        <v>6419175.697058928</v>
+        <v>6419176</v>
       </c>
       <c r="S32" t="n">
         <v>100</v>
@@ -4163,19 +4158,9 @@
           <t>1987-09-07</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>1987-09-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,12 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>106756</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109186</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4246,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436507.2332066745</v>
+        <v>436507</v>
       </c>
       <c r="R33" t="n">
-        <v>6419175.697058928</v>
+        <v>6419176</v>
       </c>
       <c r="S33" t="n">
         <v>100</v>
@@ -4279,19 +4259,9 @@
           <t>1987-09-07</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>1987-09-07</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4325,12 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4358,10 +4323,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436406.0461207972</v>
+        <v>436406</v>
       </c>
       <c r="R34" t="n">
-        <v>6419274.547413215</v>
+        <v>6419275</v>
       </c>
       <c r="S34" t="n">
         <v>100</v>
@@ -4391,19 +4356,9 @@
           <t>1994-08-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>1994-08-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4437,12 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>104540</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107007</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4474,10 +4424,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436507.2332066745</v>
+        <v>436507</v>
       </c>
       <c r="R35" t="n">
-        <v>6419175.697058928</v>
+        <v>6419176</v>
       </c>
       <c r="S35" t="n">
         <v>100</v>
@@ -4507,19 +4457,9 @@
           <t>1997-06-23</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>1997-06-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4553,12 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97514</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4590,10 +4525,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436507.2332066745</v>
+        <v>436507</v>
       </c>
       <c r="R36" t="n">
-        <v>6419175.697058928</v>
+        <v>6419176</v>
       </c>
       <c r="S36" t="n">
         <v>100</v>
@@ -4623,19 +4558,9 @@
           <t>1997-06-23</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>1997-06-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107248</v>
+        <v>107271</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109186</v>
+        <v>109210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105773</v>
+        <v>105794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107007</v>
+        <v>107030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97514</v>
+        <v>97526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107271</v>
+        <v>107283</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109210</v>
+        <v>109223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105794</v>
+        <v>105806</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107030</v>
+        <v>107042</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97526</v>
+        <v>97528</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105806</v>
+        <v>105815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107042</v>
+        <v>107051</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105815</v>
+        <v>105820</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107051</v>
+        <v>107056</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97528</v>
+        <v>97529</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105820</v>
+        <v>105848</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107056</v>
+        <v>107084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97529</v>
+        <v>97556</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107325</v>
+        <v>107338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109265</v>
+        <v>109278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105848</v>
+        <v>105861</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107084</v>
+        <v>107097</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97556</v>
+        <v>97569</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107338</v>
+        <v>107342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105861</v>
+        <v>105865</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107097</v>
+        <v>107101</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97569</v>
+        <v>97573</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4093,7 +4093,7 @@
         <v>2337603</v>
       </c>
       <c r="B32" t="n">
-        <v>107342</v>
+        <v>107350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>2642441</v>
       </c>
       <c r="B33" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>3849133</v>
       </c>
       <c r="B34" t="n">
-        <v>105865</v>
+        <v>105872</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>453603</v>
       </c>
       <c r="B35" t="n">
-        <v>107101</v>
+        <v>107109</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         <v>4531256</v>
       </c>
       <c r="B36" t="n">
-        <v>97573</v>
+        <v>97580</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,12 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107434</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4996,10 +4991,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436529.3954344561</v>
+        <v>436529</v>
       </c>
       <c r="R40" t="n">
-        <v>6419163.123649723</v>
+        <v>6419163</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5034,19 +5029,9 @@
           <t>2010-06-28</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2010-06-28</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107434</v>
+        <v>107437</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107437</v>
+        <v>107466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107466</v>
+        <v>107478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107478</v>
+        <v>107479</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107479</v>
+        <v>107484</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107484</v>
+        <v>107488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107488</v>
+        <v>107490</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4959,7 +4959,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107490</v>
+        <v>107500</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6178390</v>
+        <v>103768272</v>
       </c>
       <c r="B2" t="n">
-        <v>103429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224210</v>
+        <v>606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Mjölrödskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
+          <t>Entoloma prunuloides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo sn, Habo kommun, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436452.8915205455</v>
+        <v>436381</v>
       </c>
       <c r="R2" t="n">
-        <v>6419139.891498472</v>
+        <v>6419102</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,56 +767,50 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hårt hästbetad</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3849131</v>
+        <v>310069</v>
       </c>
       <c r="B3" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221447</v>
+        <v>803</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Lutvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Neohygrocybe nitrata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Kovalenko</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,13 +818,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R3" t="n">
-        <v>6419140.861195157</v>
+        <v>6419120</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,33 +867,33 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Bete, källa</t>
-        </is>
-      </c>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Kerstin Bergelin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>ÅGP inventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2585390</v>
+        <v>103768363</v>
       </c>
       <c r="B4" t="n">
-        <v>106963</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +901,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>803</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Lutvaxing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436493.855883633</v>
+        <v>436391</v>
       </c>
       <c r="R4" t="n">
-        <v>6419070.689803318</v>
+        <v>6419116</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +956,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,74 +982,65 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2364457</v>
+        <v>103769675</v>
       </c>
       <c r="B5" t="n">
-        <v>104837</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219955</v>
+        <v>803</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Lutvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Neohygrocybe nitrata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Kovalenko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436473.7803032578</v>
+        <v>436345</v>
       </c>
       <c r="R5" t="n">
-        <v>6419080.573521676</v>
+        <v>6419107</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,27 +1064,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Margareta Edqvist</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,36 +1080,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4536301</v>
+        <v>327766</v>
       </c>
       <c r="B6" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,34 +1107,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222112</v>
+        <v>805</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436493.855883633</v>
+        <v>436542</v>
       </c>
       <c r="R6" t="n">
-        <v>6419070.689803318</v>
+        <v>6419201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,27 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,33 +1189,29 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Betesmark-häst</t>
-        </is>
-      </c>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2672243</v>
+        <v>103819472</v>
       </c>
       <c r="B7" t="n">
-        <v>106706</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,37 +1219,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220204</v>
+        <v>805</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436473.7803032578</v>
+        <v>436397</v>
       </c>
       <c r="R7" t="n">
-        <v>6419080.573521676</v>
+        <v>6419101</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,27 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,38 +1294,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Johanne Mossberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Johanne Mossberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6000841</v>
+        <v>103768145</v>
       </c>
       <c r="B8" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,33 +1324,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223619</v>
+        <v>806</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Hygrocybe quieta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436493.855883633</v>
+        <v>436381</v>
       </c>
       <c r="R8" t="n">
-        <v>6419070.689803318</v>
+        <v>6419102</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,27 +1379,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,60 +1405,58 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3873114</v>
+        <v>271340</v>
       </c>
       <c r="B9" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221447</v>
+        <v>809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>Hygrocybe splendidissima</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1556,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436493.855883633</v>
+        <v>436542</v>
       </c>
       <c r="R9" t="n">
-        <v>6419070.689803318</v>
+        <v>6419201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,27 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,33 +1514,28 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Betesmark-häst</t>
+          <t>Betesmark med häst</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>271340</v>
+        <v>103768082</v>
       </c>
       <c r="B10" t="n">
-        <v>86165</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1547,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1678,22 +1567,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436542.2437137502</v>
+        <v>436391</v>
       </c>
       <c r="R10" t="n">
-        <v>6419201.181122187</v>
+        <v>6419116</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,22 +1607,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,36 +1633,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1229687</v>
+        <v>103769646</v>
       </c>
       <c r="B11" t="n">
-        <v>86316</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,46 +1660,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4395</v>
+        <v>809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lädervaxskivling</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cuphophyllus russocoriaceus</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436542.2437137502</v>
+        <v>436379</v>
       </c>
       <c r="R11" t="n">
-        <v>6419201.181122187</v>
+        <v>6419010</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1843,22 +1715,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,36 +1742,25 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>327766</v>
+        <v>453602</v>
       </c>
       <c r="B12" t="n">
-        <v>86156</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107664</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,43 +1768,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>805</v>
+        <v>1174</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 3, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436542.2437137502</v>
+        <v>436508</v>
       </c>
       <c r="R12" t="n">
-        <v>6419201.181122187</v>
+        <v>6419100</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,24 +1820,19 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Arkiv-F-Hab-0014</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,67 +1846,67 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr"/>
+          <t>Betesmark</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Gösta Börjeson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1275981</v>
+        <v>453603</v>
       </c>
       <c r="B13" t="n">
-        <v>88426</v>
+        <v>107664</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4373</v>
+        <v>1174</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprödvaxing</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrocybe ceracea</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Wulfen) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436453</v>
+        <v>436507</v>
       </c>
       <c r="R13" t="n">
-        <v>6419121</v>
+        <v>6419176</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2086,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2100,74 +1947,70 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Gösta Börjeson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1617733</v>
+        <v>467027</v>
       </c>
       <c r="B14" t="n">
-        <v>88460</v>
+        <v>107664</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4383</v>
+        <v>1174</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småvaxing</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436453</v>
+        <v>436503</v>
       </c>
       <c r="R14" t="n">
-        <v>6419121</v>
+        <v>6419159</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2191,12 +2034,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2004-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2004-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Antal:få Observatör Anna Lindhagen</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,76 +2053,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr"/>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anna Isaksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Via Anna Isaksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1549635</v>
+        <v>472939</v>
       </c>
       <c r="B15" t="n">
-        <v>88431</v>
+        <v>107664</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4379</v>
+        <v>1174</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Granspira</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Pedicularis sylvatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436453</v>
+        <v>436459</v>
       </c>
       <c r="R15" t="n">
-        <v>6419121</v>
+        <v>6419141</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2298,12 +2136,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2008-06-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,75 +2150,75 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1106707</v>
+        <v>437488</v>
       </c>
       <c r="B16" t="n">
-        <v>88330</v>
+        <v>83346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3297</v>
+        <v>1591</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Aprikosfingersvamp</t>
+          <t>Knubbig hårjordtunga</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Clavulinopsis luteoalba</t>
+          <t>Trichoglossum walteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Rea) Corner</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Berk.) E.J.Durand</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436453</v>
+        <v>436542</v>
       </c>
       <c r="R16" t="n">
-        <v>6419121</v>
+        <v>6419201</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2418,15 +2256,15 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2435,58 +2273,55 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1347795</v>
+        <v>576247</v>
       </c>
       <c r="B17" t="n">
-        <v>88427</v>
+        <v>110480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4374</v>
+        <v>1758</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulvaxing</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 1, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436453</v>
+        <v>436519</v>
       </c>
       <c r="R17" t="n">
-        <v>6419121</v>
+        <v>6419100</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2508,14 +2343,24 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>F-Hab-0065</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2005-07-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Mycket blad bör kollas nästa år</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,7 +2369,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2536,63 +2380,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1102068</v>
+        <v>576271</v>
       </c>
       <c r="B18" t="n">
-        <v>88328</v>
+        <v>110480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3295</v>
+        <v>1758</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Corner</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436453</v>
+        <v>436474</v>
       </c>
       <c r="R18" t="n">
-        <v>6419121</v>
+        <v>6419081</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2616,12 +2461,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,74 +2480,71 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Betesmark</t>
+          <t>Betesmark-häst</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1096544</v>
+        <v>576272</v>
       </c>
       <c r="B19" t="n">
-        <v>88344</v>
+        <v>110480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3294</v>
+        <v>1758</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ängsfingersvamp</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Clavulinopsis corniculata</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Corner</t>
+          <t>H. Lindb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436453</v>
+        <v>436459</v>
       </c>
       <c r="R19" t="n">
-        <v>6419121</v>
+        <v>6419099</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2721,12 +2568,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,76 +2582,78 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1428320</v>
+        <v>86334843</v>
       </c>
       <c r="B20" t="n">
-        <v>88429</v>
+        <v>110480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4377</v>
+        <v>1758</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blodvaxing</t>
+          <t>Fläckmaskros</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Taraxacum maculigerum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>H. Lindb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 6, Vg</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436453</v>
+        <v>436572</v>
       </c>
       <c r="R20" t="n">
-        <v>6419121</v>
+        <v>6419135</v>
       </c>
       <c r="S20" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2826,14 +2675,19 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>F-Hab-0701</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2846,30 +2700,29 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1189591</v>
+        <v>1096336</v>
       </c>
       <c r="B21" t="n">
-        <v>88383</v>
+        <v>88978</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,19 +2730,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4392</v>
+        <v>3294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Ängsfingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -2903,7 +2760,7 @@
         <v>436453</v>
       </c>
       <c r="R21" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S21" t="n">
         <v>100</v>
@@ -2968,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1248020</v>
+        <v>1102068</v>
       </c>
       <c r="B22" t="n">
-        <v>88402</v>
+        <v>88980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,20 +2836,25 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4398</v>
+        <v>3295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Clavulinopsis helvola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pers.) Corner</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3004,7 +2866,7 @@
         <v>436453</v>
       </c>
       <c r="R22" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3031,12 +2893,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2007-10-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3054,7 +2916,6 @@
           <t>Betesmark</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr"/>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -3070,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1221014</v>
+        <v>103768170</v>
       </c>
       <c r="B23" t="n">
-        <v>88452</v>
+        <v>88980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,40 +2942,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4394</v>
+        <v>3295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436453</v>
+        <v>436381</v>
       </c>
       <c r="R23" t="n">
-        <v>6419121</v>
+        <v>6419102</v>
       </c>
       <c r="S23" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3138,12 +2997,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,34 +3021,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1209184</v>
+        <v>1106707</v>
       </c>
       <c r="B24" t="n">
-        <v>88406</v>
+        <v>88982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,19 +3050,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4393</v>
+        <v>3297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling/rödgrön vaxskivling</t>
+          <t>Aprikosfingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Clavulinopsis luteoalba</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Rea) Corner</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -3213,7 +3080,7 @@
         <v>436453</v>
       </c>
       <c r="R24" t="n">
-        <v>6419121</v>
+        <v>6419120</v>
       </c>
       <c r="S24" t="n">
         <v>100</v>
@@ -3278,53 +3145,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4535752</v>
+        <v>1275981</v>
       </c>
       <c r="B25" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222112</v>
+        <v>4373</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Sprödvaxing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Hygrocybe ceracea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(Wulfen) P.Kumm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R25" t="n">
-        <v>6419140.861195157</v>
+        <v>6419120</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3348,22 +3213,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,71 +3227,75 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>472939</v>
+        <v>1347795</v>
       </c>
       <c r="B26" t="n">
-        <v>104540</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1174</v>
+        <v>4374</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436458.7635083896</v>
+        <v>436453</v>
       </c>
       <c r="R26" t="n">
-        <v>6419140.861195157</v>
+        <v>6419120</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3460,22 +3319,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2008-06-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,67 +3333,75 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3873115</v>
+        <v>1428320</v>
       </c>
       <c r="B27" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221447</v>
+        <v>4377</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Blodvaxing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436459.1625334214</v>
+        <v>436453</v>
       </c>
       <c r="R27" t="n">
-        <v>6419098.873399709</v>
+        <v>6419120</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,22 +3425,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,71 +3439,75 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4536303</v>
+        <v>1549635</v>
       </c>
       <c r="B28" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222112</v>
+        <v>4379</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436459.1625334214</v>
+        <v>436453</v>
       </c>
       <c r="R28" t="n">
-        <v>6419098.873399709</v>
+        <v>6419120</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3680,22 +3531,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,71 +3545,74 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2366753</v>
+        <v>1617733</v>
       </c>
       <c r="B29" t="n">
-        <v>104837</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89096</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219955</v>
+        <v>4383</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.E.Lange) M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436535.8438908673</v>
+        <v>436453</v>
       </c>
       <c r="R29" t="n">
-        <v>6419133.262726188</v>
+        <v>6419120</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3792,22 +3636,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,80 +3650,72 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr"/>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>481765</v>
+        <v>1189591</v>
       </c>
       <c r="B30" t="n">
-        <v>104540</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1174</v>
+        <v>4392</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Jäboruder 3, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436508.1585393944</v>
+        <v>436453</v>
       </c>
       <c r="R30" t="n">
-        <v>6419099.690997186</v>
+        <v>6419120</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3911,34 +3737,14 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>F-Hab-0069</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Kanske fler, enormt hårt bete</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3947,81 +3753,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4540051</v>
+        <v>103768155</v>
       </c>
       <c r="B31" t="n">
-        <v>95590</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222112</v>
+        <v>4392</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436535.8438908673</v>
+        <v>436381</v>
       </c>
       <c r="R31" t="n">
-        <v>6419133.262726188</v>
+        <v>6419102</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4048,22 +3839,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4078,57 +3869,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2337603</v>
+        <v>1209184</v>
       </c>
       <c r="B32" t="n">
-        <v>107353</v>
+        <v>89059</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219955</v>
+        <v>4393</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436507</v>
+        <v>436453</v>
       </c>
       <c r="R32" t="n">
-        <v>6419176</v>
+        <v>6419120</v>
       </c>
       <c r="S32" t="n">
         <v>100</v>
@@ -4155,12 +3949,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4169,67 +3963,72 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2642441</v>
+        <v>1221014</v>
       </c>
       <c r="B33" t="n">
-        <v>109293</v>
+        <v>89106</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220228</v>
+        <v>4394</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436507</v>
+        <v>436453</v>
       </c>
       <c r="R33" t="n">
-        <v>6419176</v>
+        <v>6419120</v>
       </c>
       <c r="S33" t="n">
         <v>100</v>
@@ -4256,12 +4055,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4270,66 +4069,81 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3849133</v>
+        <v>1229687</v>
       </c>
       <c r="B34" t="n">
-        <v>105875</v>
+        <v>89033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221447</v>
+        <v>4395</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Lädervaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Cuphophyllus russocoriaceus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436406</v>
+        <v>436542</v>
       </c>
       <c r="R34" t="n">
-        <v>6419275</v>
+        <v>6419201</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4353,12 +4167,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4370,64 +4184,65 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr"/>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>453603</v>
+        <v>1247452</v>
       </c>
       <c r="B35" t="n">
-        <v>107112</v>
+        <v>89035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1174</v>
+        <v>4398</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436507</v>
+        <v>436453</v>
       </c>
       <c r="R35" t="n">
-        <v>6419176</v>
+        <v>6419120</v>
       </c>
       <c r="S35" t="n">
         <v>100</v>
@@ -4454,12 +4269,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4468,70 +4283,69 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Kerstin Bergelin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>4531256</v>
+        <v>103768375</v>
       </c>
       <c r="B36" t="n">
-        <v>97583</v>
+        <v>89035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222112</v>
+        <v>4398</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436507</v>
+        <v>436391</v>
       </c>
       <c r="R36" t="n">
-        <v>6419176</v>
+        <v>6419116</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4555,12 +4369,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4575,48 +4399,39 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>467027</v>
+        <v>2337603</v>
       </c>
       <c r="B37" t="n">
-        <v>104541</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1174</v>
+        <v>219955</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granspira</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pedicularis sylvatica</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4627,17 +4442,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436502.7055573605</v>
+        <v>436507</v>
       </c>
       <c r="R37" t="n">
-        <v>6419158.763860945</v>
+        <v>6419176</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4661,27 +4476,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2004-07-14</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Antal:få Observatör Anna Lindhagen</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4696,44 +4496,43 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna Isaksson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Anna Isaksson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>75339585</v>
+        <v>2364457</v>
       </c>
       <c r="B38" t="n">
-        <v>108526</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220204</v>
+        <v>219955</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4742,23 +4541,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436529</v>
+        <v>436474</v>
       </c>
       <c r="R38" t="n">
-        <v>6419163</v>
+        <v>6419081</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4792,7 +4587,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>med Margareta Edqvist</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4801,7 +4596,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4813,7 +4607,7 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -4821,23 +4615,14 @@
           <t>Hans Thulin</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>437488</v>
+        <v>2366753</v>
       </c>
       <c r="B39" t="n">
-        <v>76591</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4845,46 +4630,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1591</v>
+        <v>219955</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knubbig hårjordtunga</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trichoglossum walteri</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Berk.) E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436542.2437137502</v>
+        <v>436536</v>
       </c>
       <c r="R39" t="n">
-        <v>6419201.181122187</v>
+        <v>6419133</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4908,22 +4684,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,21 +4701,15 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr"/>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4959,7 +4719,7 @@
         <v>75773478</v>
       </c>
       <c r="B40" t="n">
-        <v>107500</v>
+        <v>107907</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5062,15 +4822,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>310069</v>
+        <v>2672243</v>
       </c>
       <c r="B41" t="n">
-        <v>86117</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5078,21 +4833,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>803</v>
+        <v>220204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5102,13 +4857,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436453.112063889</v>
+        <v>436474</v>
       </c>
       <c r="R41" t="n">
-        <v>6419120.225843054</v>
+        <v>6419081</v>
       </c>
       <c r="S41" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5132,22 +4887,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5161,76 +4911,70 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr"/>
+          <t>Betesmark-häst</t>
+        </is>
+      </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>ÅGP inventering</t>
-        </is>
-      </c>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>576272</v>
+        <v>75339585</v>
       </c>
       <c r="B42" t="n">
-        <v>107333</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1758</v>
+        <v>220204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436459.1625334214</v>
+        <v>436529</v>
       </c>
       <c r="R42" t="n">
-        <v>6419098.873399709</v>
+        <v>6419163</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5252,24 +4996,24 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Arkiv-F-Hab-0178</t>
+        </is>
+      </c>
       <c r="Y42" t="inlineStr">
         <is>
           <t>2006-06-12</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2006-06-12</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5278,8 +5022,14 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5289,60 +5039,59 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>576271</v>
+        <v>2642441</v>
       </c>
       <c r="B43" t="n">
-        <v>107333</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1758</v>
+        <v>220228</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436473.7803032578</v>
+        <v>436507</v>
       </c>
       <c r="R43" t="n">
-        <v>6419080.573521676</v>
+        <v>6419176</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5366,27 +5115,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5397,71 +5131,69 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>576247</v>
+        <v>86334010</v>
       </c>
       <c r="B44" t="n">
-        <v>107333</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109866</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1758</v>
+        <v>220228</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäboruder 1, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436519.3450587477</v>
+        <v>436459</v>
       </c>
       <c r="R44" t="n">
-        <v>6419100.045175258</v>
+        <v>6419141</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5486,34 +5218,14 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>F-Hab-0065</t>
-        </is>
-      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Mycket blad bör kollas nästa år</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5522,6 +5234,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5533,7 +5246,7 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>F-län Floraväktarna</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -5541,23 +5254,14 @@
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>86334010</v>
+        <v>2585390</v>
       </c>
       <c r="B45" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5565,16 +5269,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220228</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5583,20 +5287,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436458.7635083896</v>
+        <v>436494</v>
       </c>
       <c r="R45" t="n">
-        <v>6419140.861195157</v>
+        <v>6419071</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5623,22 +5323,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5647,39 +5342,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Betesmark</t>
+          <t>Betesmark-häst</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>86334843</v>
+        <v>3849131</v>
       </c>
       <c r="B46" t="n">
-        <v>107333</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5687,46 +5376,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1758</v>
+        <v>221447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläckmaskros</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Taraxacum maculigerum</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>H. Lindb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Jäboruder 6, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436572.0813967428</v>
+        <v>436459</v>
       </c>
       <c r="R46" t="n">
-        <v>6419135.34599164</v>
+        <v>6419141</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5751,29 +5424,14 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>F-Hab-0701</t>
-        </is>
-      </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5782,77 +5440,67 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Bete, källa</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>103768145</v>
+        <v>3849133</v>
       </c>
       <c r="B47" t="n">
-        <v>86159</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>806</v>
+        <v>221447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luktvaxskivling</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hygrocybe quieta</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Kühner) Singer</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436381.4818315752</v>
+        <v>436406</v>
       </c>
       <c r="R47" t="n">
-        <v>6419102.23161179</v>
+        <v>6419275</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5876,22 +5524,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5906,66 +5544,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>103769665</v>
+        <v>3873114</v>
       </c>
       <c r="B48" t="n">
-        <v>86110</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>239221</v>
+        <v>221447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Papegojvaxskivling</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Schaeff.) Herink</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436345.3451666282</v>
+        <v>436494</v>
       </c>
       <c r="R48" t="n">
-        <v>6419106.525399597</v>
+        <v>6419071</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5989,22 +5626,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6015,66 +5647,65 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>103768375</v>
+        <v>3873115</v>
       </c>
       <c r="B49" t="n">
-        <v>86320</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4398</v>
+        <v>221447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit vaxskivling</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
+          <t>Gentianella campestris subsp. campestris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436391.2907674325</v>
+        <v>436459</v>
       </c>
       <c r="R49" t="n">
-        <v>6419116.424034242</v>
+        <v>6419099</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6098,22 +5729,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6128,66 +5749,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>103768170</v>
+        <v>4531256</v>
       </c>
       <c r="B50" t="n">
-        <v>85002</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3295</v>
+        <v>222112</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Corner</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436381.4818315752</v>
+        <v>436507</v>
       </c>
       <c r="R50" t="n">
-        <v>6419102.23161179</v>
+        <v>6419176</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6211,22 +5826,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6241,27 +5846,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Gösta Börjeson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>103768363</v>
+        <v>4535752</v>
       </c>
       <c r="B51" t="n">
-        <v>86117</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6269,38 +5873,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>803</v>
+        <v>222112</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436391.2907674325</v>
+        <v>436459</v>
       </c>
       <c r="R51" t="n">
-        <v>6419116.424034242</v>
+        <v>6419141</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6324,22 +5927,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6354,27 +5947,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>103768082</v>
+        <v>4536301</v>
       </c>
       <c r="B52" t="n">
-        <v>86166</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6382,47 +5970,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>809</v>
+        <v>222112</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Praktvaxskivling</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436391.2907674325</v>
+        <v>436494</v>
       </c>
       <c r="R52" t="n">
-        <v>6419116.424034242</v>
+        <v>6419071</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6446,22 +6024,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6472,66 +6045,69 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103768155</v>
+        <v>4536303</v>
       </c>
       <c r="B53" t="n">
-        <v>86314</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4392</v>
+        <v>222112</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436381.4818315752</v>
+        <v>436459</v>
       </c>
       <c r="R53" t="n">
-        <v>6419102.23161179</v>
+        <v>6419099</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6555,22 +6131,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6585,27 +6151,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>103769675</v>
+        <v>4540051</v>
       </c>
       <c r="B54" t="n">
-        <v>86117</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6613,35 +6174,43 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>803</v>
+        <v>222112</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lutvaxskivling</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neohygrocybe nitrata</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Kovalenko</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436345.3451666282</v>
+        <v>436536</v>
       </c>
       <c r="R54" t="n">
-        <v>6419106.525399597</v>
+        <v>6419133</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6668,22 +6237,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6698,27 +6257,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>103768272</v>
+        <v>4402259</v>
       </c>
       <c r="B55" t="n">
-        <v>85963</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6726,38 +6280,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>606</v>
+        <v>222133</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mjölrödskivling</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Entoloma prunuloides</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436381.4818315752</v>
+        <v>436507</v>
       </c>
       <c r="R55" t="n">
-        <v>6419102.23161179</v>
+        <v>6419176</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6781,22 +6334,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6811,72 +6354,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>103819472</v>
+        <v>6000841</v>
       </c>
       <c r="B56" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99154</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>805</v>
+        <v>223619</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436397.4421099757</v>
+        <v>436494</v>
       </c>
       <c r="R56" t="n">
-        <v>6419101.446833832</v>
+        <v>6419071</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6900,22 +6431,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6924,22 +6450,431 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johanne Mossberg</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johanne Mossberg</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6178390</v>
+      </c>
+      <c r="B57" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Jäboruder, Habo sn, Habo kommun, Vg</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>436453</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6419140</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2003-06-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2003-06-23</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Hårt hästbetad</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>103769665</v>
+      </c>
+      <c r="B58" t="n">
+        <v>89060</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>239221</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Gliophorus psittacinus var. psittacinus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>436345</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6419107</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>6733761</v>
+      </c>
+      <c r="B59" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>436474</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6419081</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Hans Thulin</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>86334003</v>
+      </c>
+      <c r="B60" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Jäboruder, Vg</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>436459</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6419141</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Habo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2020-06-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
           <t>ÅGP inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/310069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768363</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103769675</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/327766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103819472</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,6 +1453,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768145</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/271340</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1646,6 +1691,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768082</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103769646</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/453602</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/453603</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/467027</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2165,6 +2235,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/472939</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437488</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/576247</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/576271</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/576272</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2714,6 +2809,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86334843</t>
         </is>
       </c>
     </row>
@@ -2822,6 +2922,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1096336</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2928,6 +3033,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1102068</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3036,6 +3146,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768170</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3142,6 +3257,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1106707</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3248,6 +3368,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1275981</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3354,6 +3479,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1347795</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3460,6 +3590,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1428320</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3566,6 +3701,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1549635</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3672,6 +3812,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1617733</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3774,6 +3919,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1189591</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3878,6 +4028,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768155</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3984,6 +4139,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1209184</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4090,6 +4250,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1221014</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4202,6 +4367,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1229687</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4304,6 +4474,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1247452</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4408,6 +4583,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103768375</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4509,6 +4689,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2337603</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4616,6 +4801,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2364457</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4713,6 +4903,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2366753</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4819,6 +5014,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75773478</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4926,6 +5126,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2672243</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5047,6 +5252,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75339585</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5146,6 +5356,11 @@
       <c r="AY43" t="inlineStr">
         <is>
           <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2642441</t>
         </is>
       </c>
     </row>
@@ -5255,6 +5470,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86334010</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5362,6 +5582,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2585390</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5460,6 +5685,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3849131</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5557,6 +5787,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3849133</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5665,6 +5900,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3873114</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5758,6 +5998,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3873115</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5859,6 +6104,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4531256</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5956,6 +6206,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4535752</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6063,6 +6318,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4536301</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6160,6 +6420,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4536303</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6266,6 +6531,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4540051</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6367,6 +6637,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4402259</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6470,6 +6745,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6000841</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6576,6 +6856,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6178390</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6665,6 +6950,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103769665</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6772,6 +7062,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6733761</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6875,8 +7170,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86334003</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4147,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1221014</v>
+        <v>103769665</v>
       </c>
       <c r="B33" t="n">
-        <v>89106</v>
+        <v>89206</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4158,40 +4158,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4394</v>
+        <v>4393</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Honungsvaxing</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hygrocybe reidii</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kühner</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436453</v>
+        <v>436345</v>
       </c>
       <c r="R33" t="n">
-        <v>6419120</v>
+        <v>6419107</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4215,12 +4213,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4229,86 +4227,74 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1221014</t>
+          <t>https://artportalen.se/Sighting/103769665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1229687</v>
+        <v>1221014</v>
       </c>
       <c r="B34" t="n">
-        <v>89033</v>
+        <v>89106</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4395</v>
+        <v>4394</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lädervaxing</t>
+          <t>Honungsvaxing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cuphophyllus russocoriaceus</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Kühner</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436542</v>
+        <v>436453</v>
       </c>
       <c r="R34" t="n">
-        <v>6419201</v>
+        <v>6419120</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,15 +4332,15 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Betesmark med häst</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr"/>
+          <t>Betesmark</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4363,59 +4349,69 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin, Niklas Johansson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1229687</t>
+          <t>https://artportalen.se/Sighting/1221014</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1247452</v>
+        <v>1229687</v>
       </c>
       <c r="B35" t="n">
-        <v>89035</v>
+        <v>89033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4398</v>
+        <v>4395</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Lädervaxing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>Cuphophyllus russocoriaceus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; Jos.K.Miller) Bon</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436453</v>
+        <v>436542</v>
       </c>
       <c r="R35" t="n">
-        <v>6419120</v>
+        <v>6419201</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4453,15 +4449,15 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Betesmark</t>
-        </is>
-      </c>
+          <t>Betesmark med häst</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr"/>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4470,19 +4466,19 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kerstin Bergelin</t>
+          <t>Kerstin Bergelin, Niklas Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1247452</t>
+          <t>https://artportalen.se/Sighting/1229687</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103768375</v>
+        <v>1247452</v>
       </c>
       <c r="B36" t="n">
         <v>89035</v>
@@ -4507,20 +4503,22 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436391</v>
+        <v>436453</v>
       </c>
       <c r="R36" t="n">
-        <v>6419116</v>
+        <v>6419120</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4544,22 +4542,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4568,71 +4556,74 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Kerstin Bergelin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103768375</t>
+          <t>https://artportalen.se/Sighting/1247452</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2337603</v>
+        <v>103768375</v>
       </c>
       <c r="B37" t="n">
-        <v>107908</v>
+        <v>89035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219955</v>
+        <v>4398</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436507</v>
+        <v>436391</v>
       </c>
       <c r="R37" t="n">
-        <v>6419176</v>
+        <v>6419116</v>
       </c>
       <c r="S37" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4656,12 +4647,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2022-09-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4676,28 +4677,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anders Hildingsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Anders Hildingsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2337603</t>
+          <t>https://artportalen.se/Sighting/103768375</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2364457</v>
+        <v>2337603</v>
       </c>
       <c r="B38" t="n">
         <v>107908</v>
@@ -4728,17 +4725,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436474</v>
+        <v>436507</v>
       </c>
       <c r="R38" t="n">
-        <v>6419081</v>
+        <v>6419176</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,17 +4759,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Margareta Edqvist</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4783,33 +4775,32 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2364457</t>
+          <t>https://artportalen.se/Sighting/2337603</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2366753</v>
+        <v>2364457</v>
       </c>
       <c r="B39" t="n">
         <v>107908</v>
@@ -4844,13 +4835,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436536</v>
+        <v>436474</v>
       </c>
       <c r="R39" t="n">
-        <v>6419133</v>
+        <v>6419081</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4874,12 +4865,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4890,31 +4886,36 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2366753</t>
+          <t>https://artportalen.se/Sighting/2364457</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>75773478</v>
+        <v>2366753</v>
       </c>
       <c r="B40" t="n">
-        <v>107907</v>
+        <v>107908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4942,17 +4943,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Jäboruder 5, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436529</v>
+        <v>436536</v>
       </c>
       <c r="R40" t="n">
-        <v>6419163</v>
+        <v>6419133</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4972,11 +4973,6 @@
       <c r="W40" t="inlineStr">
         <is>
           <t>Habo</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>F-Hab-0342</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5006,43 +5002,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75773478</t>
+          <t>https://artportalen.se/Sighting/2366753</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2672243</v>
+        <v>75773478</v>
       </c>
       <c r="B41" t="n">
-        <v>109815</v>
+        <v>107907</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220204</v>
+        <v>219955</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5053,14 +5045,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder 5, Vg</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436474</v>
+        <v>436529</v>
       </c>
       <c r="R41" t="n">
-        <v>6419081</v>
+        <v>6419163</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5085,19 +5077,19 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>F-Hab-0342</t>
+        </is>
+      </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5108,33 +5100,32 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2672243</t>
+          <t>https://artportalen.se/Sighting/75773478</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>75339585</v>
+        <v>2672243</v>
       </c>
       <c r="B42" t="n">
         <v>109815</v>
@@ -5163,23 +5154,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436529</v>
+        <v>436474</v>
       </c>
       <c r="R42" t="n">
-        <v>6419163</v>
+        <v>6419081</v>
       </c>
       <c r="S42" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5201,11 +5188,6 @@
           <t>Habo</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Arkiv-F-Hab-0178</t>
-        </is>
-      </c>
       <c r="Y42" t="inlineStr">
         <is>
           <t>2006-06-12</t>
@@ -5227,7 +5209,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5239,7 +5220,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5247,23 +5228,19 @@
           <t>Hans Thulin</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75339585</t>
+          <t>https://artportalen.se/Sighting/2672243</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2642441</v>
+        <v>75339585</v>
       </c>
       <c r="B43" t="n">
-        <v>109866</v>
+        <v>109815</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5271,16 +5248,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220228</v>
+        <v>220204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5289,16 +5266,20 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436507</v>
+        <v>436529</v>
       </c>
       <c r="R43" t="n">
-        <v>6419176</v>
+        <v>6419163</v>
       </c>
       <c r="S43" t="n">
         <v>100</v>
@@ -5323,14 +5304,24 @@
           <t>Habo</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Arkiv-F-Hab-0178</t>
+        </is>
+      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,34 +5330,40 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Västergötlands flora 2002</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2642441</t>
+          <t>https://artportalen.se/Sighting/75339585</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>86334010</v>
+        <v>2642441</v>
       </c>
       <c r="B44" t="n">
         <v>109866</v>
@@ -5395,23 +5392,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436459</v>
+        <v>436507</v>
       </c>
       <c r="R44" t="n">
-        <v>6419141</v>
+        <v>6419176</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5435,12 +5428,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2020-06-14</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5449,39 +5442,37 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Betesmark</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86334010</t>
+          <t>https://artportalen.se/Sighting/2642441</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2585390</v>
+        <v>86334010</v>
       </c>
       <c r="B45" t="n">
-        <v>110078</v>
+        <v>109866</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5489,16 +5480,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>220228</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5507,16 +5498,20 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436494</v>
+        <v>436459</v>
       </c>
       <c r="R45" t="n">
-        <v>6419071</v>
+        <v>6419141</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5543,17 +5538,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2020-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5562,58 +5552,63 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Betesmark-häst</t>
+          <t>Betesmark</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2585390</t>
+          <t>https://artportalen.se/Sighting/86334010</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3849131</v>
+        <v>2585390</v>
       </c>
       <c r="B46" t="n">
-        <v>106414</v>
+        <v>110078</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221447</v>
+        <v>220299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5621,10 +5616,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436459</v>
+        <v>436494</v>
       </c>
       <c r="R46" t="n">
-        <v>6419141</v>
+        <v>6419071</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5651,12 +5646,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>1994-08-01</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5670,30 +5670,30 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Bete, källa</t>
+          <t>Betesmark-häst</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3849131</t>
+          <t>https://artportalen.se/Sighting/2585390</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3849133</v>
+        <v>3849131</v>
       </c>
       <c r="B47" t="n">
         <v>106414</v>
@@ -5720,17 +5720,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436406</v>
+        <v>436459</v>
       </c>
       <c r="R47" t="n">
-        <v>6419275</v>
+        <v>6419141</v>
       </c>
       <c r="S47" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5770,11 +5770,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Bete, källa</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Anders Bertilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -5782,20 +5787,16 @@
           <t>Anders Bertilsson</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3849133</t>
+          <t>https://artportalen.se/Sighting/3849131</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3873114</v>
+        <v>3849133</v>
       </c>
       <c r="B48" t="n">
         <v>106414</v>
@@ -5820,24 +5821,19 @@
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete, källa 250 m N om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436494</v>
+        <v>436406</v>
       </c>
       <c r="R48" t="n">
-        <v>6419071</v>
+        <v>6419275</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5861,17 +5857,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>1994-08-01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5882,33 +5873,32 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3873114</t>
+          <t>https://artportalen.se/Sighting/3849133</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3873115</v>
+        <v>3873114</v>
       </c>
       <c r="B49" t="n">
         <v>106414</v>
@@ -5933,19 +5923,24 @@
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436459</v>
+        <v>436494</v>
       </c>
       <c r="R49" t="n">
-        <v>6419099</v>
+        <v>6419071</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5977,6 +5972,11 @@
           <t>2006-06-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5985,69 +5985,70 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3873115</t>
+          <t>https://artportalen.se/Sighting/3873114</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4531256</v>
+        <v>3873115</v>
       </c>
       <c r="B50" t="n">
-        <v>98050</v>
+        <v>106414</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222112</v>
+        <v>221447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436507</v>
+        <v>436459</v>
       </c>
       <c r="R50" t="n">
-        <v>6419176</v>
+        <v>6419099</v>
       </c>
       <c r="S50" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6071,12 +6072,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1997-06-23</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6091,28 +6092,24 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Gösta Börjeson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4531256</t>
+          <t>https://artportalen.se/Sighting/3873115</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4535752</v>
+        <v>4531256</v>
       </c>
       <c r="B51" t="n">
         <v>98050</v>
@@ -6143,17 +6140,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>betesmark 200 m NNO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436459</v>
+        <v>436507</v>
       </c>
       <c r="R51" t="n">
-        <v>6419141</v>
+        <v>6419176</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6177,12 +6174,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2005-07-26</t>
+          <t>1997-06-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6197,24 +6194,28 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Gösta Börjeson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4535752</t>
+          <t>https://artportalen.se/Sighting/4531256</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4536301</v>
+        <v>4535752</v>
       </c>
       <c r="B52" t="n">
         <v>98050</v>
@@ -6249,13 +6250,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436494</v>
+        <v>436459</v>
       </c>
       <c r="R52" t="n">
-        <v>6419071</v>
+        <v>6419141</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6279,17 +6280,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>2005-07-26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6300,33 +6296,28 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4536301</t>
+          <t>https://artportalen.se/Sighting/4535752</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4536303</v>
+        <v>4536301</v>
       </c>
       <c r="B53" t="n">
         <v>98050</v>
@@ -6361,13 +6352,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436459</v>
+        <v>436494</v>
       </c>
       <c r="R53" t="n">
-        <v>6419099</v>
+        <v>6419071</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6399,6 +6390,11 @@
           <t>2006-06-12</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6407,28 +6403,33 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Betesmark-häst</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4536303</t>
+          <t>https://artportalen.se/Sighting/4536301</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4540051</v>
+        <v>4536303</v>
       </c>
       <c r="B54" t="n">
         <v>98050</v>
@@ -6456,29 +6457,20 @@
           <t>(L.) Sw.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>436536</v>
+        <v>436459</v>
       </c>
       <c r="R54" t="n">
-        <v>6419133</v>
+        <v>6419099</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6502,12 +6494,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2010-06-28</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6533,16 +6525,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4540051</t>
+          <t>https://artportalen.se/Sighting/4536303</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4402259</v>
+        <v>4540051</v>
       </c>
       <c r="B55" t="n">
-        <v>102560</v>
+        <v>98050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6550,37 +6542,46 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222133</v>
+        <v>222112</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jungfrulin</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Polygala vulgaris</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bete mm NO om JÄBORUDER, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>436507</v>
+        <v>436536</v>
       </c>
       <c r="R55" t="n">
-        <v>6419176</v>
+        <v>6419133</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6604,12 +6605,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>1987-09-07</t>
+          <t>2010-06-28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6624,65 +6625,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4402259</t>
+          <t>https://artportalen.se/Sighting/4540051</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>6000841</v>
+        <v>4402259</v>
       </c>
       <c r="B56" t="n">
-        <v>99154</v>
+        <v>102560</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>223619</v>
+        <v>222133</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Bete mm NO om JÄBORUDER, Vg</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>436494</v>
+        <v>436507</v>
       </c>
       <c r="R56" t="n">
-        <v>6419071</v>
+        <v>6419176</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6706,17 +6707,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2006-06-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>med Margareta Edqvist</t>
+          <t>1987-09-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6727,75 +6723,66 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Betesmark-häst</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Hans Thulin</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6000841</t>
+          <t>https://artportalen.se/Sighting/4402259</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>6178390</v>
+        <v>6000841</v>
       </c>
       <c r="B57" t="n">
-        <v>106417</v>
+        <v>99154</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>224210</v>
+        <v>223619</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tidig fältgentiana</t>
+          <t>Ängsnattviol</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. suecica</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Froel.) Dostál</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Jäboruder, Habo sn, Habo kommun, Vg</t>
+          <t>Jäboruder, Vg</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>436453</v>
+        <v>436494</v>
       </c>
       <c r="R57" t="n">
-        <v>6419140</v>
+        <v>6419071</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6822,12 +6809,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2006-06-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2006-06-12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>med Margareta Edqvist</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6841,63 +6833,75 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>Hårt hästbetad</t>
+          <t>Betesmark-häst</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Hans Thulin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6178390</t>
+          <t>https://artportalen.se/Sighting/6000841</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>103769665</v>
+        <v>6178390</v>
       </c>
       <c r="B58" t="n">
-        <v>89060</v>
+        <v>106417</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>239221</v>
+        <v>224210</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Jäboruder, Vg</t>
+          <t>Jäboruder, Habo sn, Habo kommun, Vg</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>436345</v>
+        <v>436453</v>
       </c>
       <c r="R58" t="n">
-        <v>6419107</v>
+        <v>6419140</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6921,12 +6925,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2003-06-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2003-06-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6937,22 +6941,27 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Hårt hästbetad</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Hildingsson</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103769665</t>
+          <t>https://artportalen.se/Sighting/6178390</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4150,7 +4150,7 @@
         <v>103769665</v>
       </c>
       <c r="B33" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
